--- a/Översikt SKÖVDE.xlsx
+++ b/Översikt SKÖVDE.xlsx
@@ -601,7 +601,7 @@
         <v>46196</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -736,7 +736,7 @@
         <v>46198</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -852,7 +852,7 @@
         <v>45876</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -966,7 +966,7 @@
         <v>45743</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1080,7 +1080,7 @@
         <v>46182</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1190,7 +1190,7 @@
         <v>44495</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1300,7 +1300,7 @@
         <v>45201</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1409,7 +1409,7 @@
         <v>46014</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1518,7 +1518,7 @@
         <v>46080</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1627,7 +1627,7 @@
         <v>44595</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1744,7 +1744,7 @@
         <v>44594</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1861,7 +1861,7 @@
         <v>45306</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1977,7 +1977,7 @@
         <v>45979</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2089,7 +2089,7 @@
         <v>45714</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2206,7 +2206,7 @@
         <v>44949</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2323,7 +2323,7 @@
         <v>45387</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2431,7 +2431,7 @@
         <v>44928</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2543,7 +2543,7 @@
         <v>45334</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2654,7 +2654,7 @@
         <v>45334</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2765,7 +2765,7 @@
         <v>44943</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2872,7 +2872,7 @@
         <v>44804</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2984,7 +2984,7 @@
         <v>44817</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3091,7 +3091,7 @@
         <v>44837</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3198,7 +3198,7 @@
         <v>45506</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3305,7 +3305,7 @@
         <v>45824</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3417,7 +3417,7 @@
         <v>45799</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3528,7 +3528,7 @@
         <v>45903</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3639,7 +3639,7 @@
         <v>45635</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3745,7 +3745,7 @@
         <v>45972</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3851,7 +3851,7 @@
         <v>44988</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3962,7 +3962,7 @@
         <v>45797</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4077,7 +4077,7 @@
         <v>46185</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4183,7 +4183,7 @@
         <v>44495</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4289,7 +4289,7 @@
         <v>44750</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4400,7 +4400,7 @@
         <v>45785</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4510,7 +4510,7 @@
         <v>45743</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4616,7 +4616,7 @@
         <v>45471</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4722,7 +4722,7 @@
         <v>45800</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4833,7 +4833,7 @@
         <v>44834</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4943,7 +4943,7 @@
         <v>44475</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5048,7 +5048,7 @@
         <v>44988</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5153,7 +5153,7 @@
         <v>45019</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5258,7 +5258,7 @@
         <v>45148</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5363,7 +5363,7 @@
         <v>45755</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5473,7 +5473,7 @@
         <v>45322</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5578,7 +5578,7 @@
         <v>45932</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5683,7 +5683,7 @@
         <v>45204</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5788,7 +5788,7 @@
         <v>46198</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5893,7 +5893,7 @@
         <v>45645</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5998,7 +5998,7 @@
         <v>45182</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6108,7 +6108,7 @@
         <v>45224</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6213,7 +6213,7 @@
         <v>46045</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6318,7 +6318,7 @@
         <v>46052</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6423,7 +6423,7 @@
         <v>45104</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6533,7 +6533,7 @@
         <v>46173</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6638,7 +6638,7 @@
         <v>45040</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6743,7 +6743,7 @@
         <v>45036</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6848,7 +6848,7 @@
         <v>45322</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6953,7 +6953,7 @@
         <v>46272</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7058,7 +7058,7 @@
         <v>45810</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7168,7 +7168,7 @@
         <v>44986</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7278,7 +7278,7 @@
         <v>44594</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7356,7 +7356,7 @@
         <v>44609</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7429,7 +7429,7 @@
         <v>44543</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7507,7 +7507,7 @@
         <v>44516</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7580,7 +7580,7 @@
         <v>44844</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7653,7 +7653,7 @@
         <v>44567</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7726,7 +7726,7 @@
         <v>44523</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7799,7 +7799,7 @@
         <v>44748</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7872,7 +7872,7 @@
         <v>44748</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7945,7 +7945,7 @@
         <v>44585</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8018,7 +8018,7 @@
         <v>44614</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8096,7 +8096,7 @@
         <v>44698</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8169,7 +8169,7 @@
         <v>44740</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8242,7 +8242,7 @@
         <v>44530</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8315,7 +8315,7 @@
         <v>44698</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8388,7 +8388,7 @@
         <v>44847</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8461,7 +8461,7 @@
         <v>44635</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8534,7 +8534,7 @@
         <v>44823</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8607,7 +8607,7 @@
         <v>44629</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8680,7 +8680,7 @@
         <v>44481</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8753,7 +8753,7 @@
         <v>44762</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8826,7 +8826,7 @@
         <v>44809</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8899,7 +8899,7 @@
         <v>44743</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8972,7 +8972,7 @@
         <v>45201</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9045,7 +9045,7 @@
         <v>45197</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9118,7 +9118,7 @@
         <v>45322</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9191,7 +9191,7 @@
         <v>44959</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9264,7 +9264,7 @@
         <v>45749</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9342,7 +9342,7 @@
         <v>45721</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9415,7 +9415,7 @@
         <v>44903</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9493,7 +9493,7 @@
         <v>44601</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9571,7 +9571,7 @@
         <v>45230</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9644,7 +9644,7 @@
         <v>45539</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9717,7 +9717,7 @@
         <v>45093</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9790,7 +9790,7 @@
         <v>45163</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9863,7 +9863,7 @@
         <v>45215</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9936,7 +9936,7 @@
         <v>45161</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10009,7 +10009,7 @@
         <v>45699</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10087,7 +10087,7 @@
         <v>45385</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10160,7 +10160,7 @@
         <v>44523</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10238,7 +10238,7 @@
         <v>45439</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10311,7 +10311,7 @@
         <v>44862</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10384,7 +10384,7 @@
         <v>45259</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10457,7 +10457,7 @@
         <v>45594</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10530,7 +10530,7 @@
         <v>45267</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10603,7 +10603,7 @@
         <v>45670</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10676,7 +10676,7 @@
         <v>45693</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10749,7 +10749,7 @@
         <v>45884</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10827,7 +10827,7 @@
         <v>45853</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10900,7 +10900,7 @@
         <v>45888</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10978,7 +10978,7 @@
         <v>45889</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11051,7 +11051,7 @@
         <v>45889</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11124,7 +11124,7 @@
         <v>45635</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11197,7 +11197,7 @@
         <v>45301</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11270,7 +11270,7 @@
         <v>45204</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11343,7 +11343,7 @@
         <v>45709</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11416,7 +11416,7 @@
         <v>45756</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11489,7 +11489,7 @@
         <v>45211</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11562,7 +11562,7 @@
         <v>45376</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11635,7 +11635,7 @@
         <v>44586</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11708,7 +11708,7 @@
         <v>45530</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11781,7 +11781,7 @@
         <v>45401</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11854,7 +11854,7 @@
         <v>44963</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11927,7 +11927,7 @@
         <v>45929</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12000,7 +12000,7 @@
         <v>44938</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12073,7 +12073,7 @@
         <v>45138</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12146,7 +12146,7 @@
         <v>45320</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12219,7 +12219,7 @@
         <v>45905</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12292,7 +12292,7 @@
         <v>44495</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12365,7 +12365,7 @@
         <v>45932</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12438,7 +12438,7 @@
         <v>45937</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12511,7 +12511,7 @@
         <v>44600</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12584,7 +12584,7 @@
         <v>44739</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12657,7 +12657,7 @@
         <v>45560</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12730,7 +12730,7 @@
         <v>46149</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12803,7 +12803,7 @@
         <v>45947</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12876,7 +12876,7 @@
         <v>45947</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12949,7 +12949,7 @@
         <v>45947</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13022,7 +13022,7 @@
         <v>45693</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13095,7 +13095,7 @@
         <v>45306</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13168,7 +13168,7 @@
         <v>45953</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13246,7 +13246,7 @@
         <v>45531</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13319,7 +13319,7 @@
         <v>45958</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13392,7 +13392,7 @@
         <v>45324</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13465,7 +13465,7 @@
         <v>45245</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13538,7 +13538,7 @@
         <v>45636</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13611,7 +13611,7 @@
         <v>45694</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13684,7 +13684,7 @@
         <v>45315</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13757,7 +13757,7 @@
         <v>45989</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13835,7 +13835,7 @@
         <v>45989</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13913,7 +13913,7 @@
         <v>45013</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13986,7 +13986,7 @@
         <v>45586</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14059,7 +14059,7 @@
         <v>46139</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14132,7 +14132,7 @@
         <v>45086</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14205,7 +14205,7 @@
         <v>45267</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14278,7 +14278,7 @@
         <v>45006</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14351,7 +14351,7 @@
         <v>46038</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14424,7 +14424,7 @@
         <v>46001</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14497,7 +14497,7 @@
         <v>46001</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14570,7 +14570,7 @@
         <v>46001</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14643,7 +14643,7 @@
         <v>44796</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14716,7 +14716,7 @@
         <v>46002</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14789,7 +14789,7 @@
         <v>46002</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14862,7 +14862,7 @@
         <v>46008</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14935,7 +14935,7 @@
         <v>46008</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15008,7 +15008,7 @@
         <v>45076</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15081,7 +15081,7 @@
         <v>46013</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15154,7 +15154,7 @@
         <v>45742</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15227,7 +15227,7 @@
         <v>46017</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15300,7 +15300,7 @@
         <v>44599</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15378,7 +15378,7 @@
         <v>44750</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15456,7 +15456,7 @@
         <v>44636</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15529,7 +15529,7 @@
         <v>44462</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15602,7 +15602,7 @@
         <v>45105</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15675,7 +15675,7 @@
         <v>46036</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15748,7 +15748,7 @@
         <v>45314</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15821,7 +15821,7 @@
         <v>46174</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15894,7 +15894,7 @@
         <v>45259</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15967,7 +15967,7 @@
         <v>46051</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16040,7 +16040,7 @@
         <v>46052</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16113,7 +16113,7 @@
         <v>44938</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16186,7 +16186,7 @@
         <v>45992</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16259,7 +16259,7 @@
         <v>46010</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16337,7 +16337,7 @@
         <v>46062</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16410,7 +16410,7 @@
         <v>46010</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16488,7 +16488,7 @@
         <v>46009</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16566,7 +16566,7 @@
         <v>46009</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16644,7 +16644,7 @@
         <v>46062</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16717,7 +16717,7 @@
         <v>46182</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16790,7 +16790,7 @@
         <v>46182</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16863,7 +16863,7 @@
         <v>44820</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16936,7 +16936,7 @@
         <v>45299</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17009,7 +17009,7 @@
         <v>46185</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17082,7 +17082,7 @@
         <v>45169</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17155,7 +17155,7 @@
         <v>45093</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17228,7 +17228,7 @@
         <v>45590</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17301,7 +17301,7 @@
         <v>46091</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17374,7 +17374,7 @@
         <v>45586</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17447,7 +17447,7 @@
         <v>45082</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17520,7 +17520,7 @@
         <v>45687</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17593,7 +17593,7 @@
         <v>46099</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17666,7 +17666,7 @@
         <v>45138</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17739,7 +17739,7 @@
         <v>45134</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17812,7 +17812,7 @@
         <v>46202</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17885,7 +17885,7 @@
         <v>45590</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17958,7 +17958,7 @@
         <v>45418</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -18031,7 +18031,7 @@
         <v>45301</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -18104,7 +18104,7 @@
         <v>45894</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -18177,7 +18177,7 @@
         <v>45685</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18250,7 +18250,7 @@
         <v>45847</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18323,7 +18323,7 @@
         <v>44811</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18396,7 +18396,7 @@
         <v>45706</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18469,7 +18469,7 @@
         <v>45210</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18542,7 +18542,7 @@
         <v>46253</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18615,7 +18615,7 @@
         <v>45002</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18688,7 +18688,7 @@
         <v>45706</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18761,7 +18761,7 @@
         <v>44825</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18834,7 +18834,7 @@
         <v>45590</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18907,7 +18907,7 @@
         <v>46129</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18980,7 +18980,7 @@
         <v>44804</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -19053,7 +19053,7 @@
         <v>45159</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -19126,7 +19126,7 @@
         <v>45306</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -19199,7 +19199,7 @@
         <v>45721</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19272,7 +19272,7 @@
         <v>45315</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19345,7 +19345,7 @@
         <v>45737</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19418,7 +19418,7 @@
         <v>45547</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19491,7 +19491,7 @@
         <v>45775</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19564,7 +19564,7 @@
         <v>46269</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19637,7 +19637,7 @@
         <v>46272</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19710,7 +19710,7 @@
         <v>45715</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19783,7 +19783,7 @@
         <v>45743</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19856,7 +19856,7 @@
         <v>45710</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19929,7 +19929,7 @@
         <v>45792</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20002,7 +20002,7 @@
         <v>45334</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -20075,7 +20075,7 @@
         <v>45142</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -20148,7 +20148,7 @@
         <v>45734</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20226,7 +20226,7 @@
         <v>46283</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20299,7 +20299,7 @@
         <v>45796</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20372,7 +20372,7 @@
         <v>45799</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20450,7 +20450,7 @@
         <v>45799</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20528,7 +20528,7 @@
         <v>45803</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20601,7 +20601,7 @@
         <v>45800</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20679,7 +20679,7 @@
         <v>45800</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20752,7 +20752,7 @@
         <v>45810</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20825,7 +20825,7 @@
         <v>45810</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20898,7 +20898,7 @@
         <v>45810</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20971,7 +20971,7 @@
         <v>45821</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -21044,7 +21044,7 @@
         <v>45821</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -21117,7 +21117,7 @@
         <v>45824</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -21195,7 +21195,7 @@
         <v>45821</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -21268,7 +21268,7 @@
         <v>45821</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -21341,7 +21341,7 @@
         <v>45827</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21419,7 +21419,7 @@
         <v>45840</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21492,7 +21492,7 @@
         <v>45842</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21565,7 +21565,7 @@
         <v>45846</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21638,7 +21638,7 @@
         <v>45846</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21711,7 +21711,7 @@
         <v>45846</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21784,7 +21784,7 @@
         <v>45769</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21857,7 +21857,7 @@
         <v>44986</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21955,7 +21955,7 @@
         <v>45716</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>

--- a/Översikt SKÖVDE.xlsx
+++ b/Översikt SKÖVDE.xlsx
@@ -601,7 +601,7 @@
         <v>46196</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -736,7 +736,7 @@
         <v>46198</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -852,7 +852,7 @@
         <v>45876</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -966,7 +966,7 @@
         <v>45743</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1080,7 +1080,7 @@
         <v>46182</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1190,7 +1190,7 @@
         <v>44495</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1300,7 +1300,7 @@
         <v>45201</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1409,7 +1409,7 @@
         <v>46080</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1518,7 +1518,7 @@
         <v>46014</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1627,7 +1627,7 @@
         <v>44595</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1744,7 +1744,7 @@
         <v>44594</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1861,7 +1861,7 @@
         <v>45306</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1977,7 +1977,7 @@
         <v>44949</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2094,7 +2094,7 @@
         <v>45979</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2206,7 +2206,7 @@
         <v>45714</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2323,7 +2323,7 @@
         <v>45387</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2431,7 +2431,7 @@
         <v>44837</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2538,7 +2538,7 @@
         <v>44804</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2650,7 +2650,7 @@
         <v>45506</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2757,7 +2757,7 @@
         <v>45824</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2869,7 +2869,7 @@
         <v>45334</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2980,7 +2980,7 @@
         <v>45334</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3091,7 +3091,7 @@
         <v>44943</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3198,7 +3198,7 @@
         <v>44817</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3305,7 +3305,7 @@
         <v>46289</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3412,7 +3412,7 @@
         <v>44928</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3524,7 +3524,7 @@
         <v>45800</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3635,7 +3635,7 @@
         <v>45471</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3741,7 +3741,7 @@
         <v>45972</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3847,7 +3847,7 @@
         <v>44495</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3953,7 +3953,7 @@
         <v>45799</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4064,7 +4064,7 @@
         <v>45797</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4179,7 +4179,7 @@
         <v>44988</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4290,7 +4290,7 @@
         <v>46185</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4396,7 +4396,7 @@
         <v>45903</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4507,7 +4507,7 @@
         <v>44750</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4618,7 +4618,7 @@
         <v>45635</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4724,7 +4724,7 @@
         <v>45785</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4834,7 +4834,7 @@
         <v>45743</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4940,7 +4940,7 @@
         <v>44834</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5050,7 +5050,7 @@
         <v>44475</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5155,7 +5155,7 @@
         <v>46045</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5260,7 +5260,7 @@
         <v>46052</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5365,7 +5365,7 @@
         <v>45810</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5475,7 +5475,7 @@
         <v>45932</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5580,7 +5580,7 @@
         <v>45645</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5685,7 +5685,7 @@
         <v>45322</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5790,7 +5790,7 @@
         <v>45755</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5900,7 +5900,7 @@
         <v>46198</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6005,7 +6005,7 @@
         <v>45104</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6115,7 +6115,7 @@
         <v>45019</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6220,7 +6220,7 @@
         <v>44988</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6325,7 +6325,7 @@
         <v>45204</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6430,7 +6430,7 @@
         <v>46173</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6535,7 +6535,7 @@
         <v>45224</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6640,7 +6640,7 @@
         <v>46272</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6745,7 +6745,7 @@
         <v>45036</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6850,7 +6850,7 @@
         <v>45040</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6955,7 +6955,7 @@
         <v>45148</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7060,7 +7060,7 @@
         <v>45182</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7170,7 +7170,7 @@
         <v>45322</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7275,7 +7275,7 @@
         <v>44986</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7385,7 +7385,7 @@
         <v>44594</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7463,7 +7463,7 @@
         <v>44609</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7536,7 +7536,7 @@
         <v>44543</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7614,7 +7614,7 @@
         <v>44516</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7687,7 +7687,7 @@
         <v>44844</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7760,7 +7760,7 @@
         <v>44567</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7833,7 +7833,7 @@
         <v>44523</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7906,7 +7906,7 @@
         <v>44748</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7979,7 +7979,7 @@
         <v>44748</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8052,7 +8052,7 @@
         <v>44585</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8125,7 +8125,7 @@
         <v>44614</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8203,7 +8203,7 @@
         <v>44698</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8276,7 +8276,7 @@
         <v>44740</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8349,7 +8349,7 @@
         <v>44530</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8422,7 +8422,7 @@
         <v>44698</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8495,7 +8495,7 @@
         <v>44847</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8568,7 +8568,7 @@
         <v>44635</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8641,7 +8641,7 @@
         <v>44823</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8714,7 +8714,7 @@
         <v>44629</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8787,7 +8787,7 @@
         <v>44481</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8860,7 +8860,7 @@
         <v>44762</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8933,7 +8933,7 @@
         <v>44809</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9006,7 +9006,7 @@
         <v>45267</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9079,7 +9079,7 @@
         <v>45322</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9152,7 +9152,7 @@
         <v>44862</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9225,7 +9225,7 @@
         <v>45138</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9298,7 +9298,7 @@
         <v>45299</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9371,7 +9371,7 @@
         <v>45301</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9444,7 +9444,7 @@
         <v>45245</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9517,7 +9517,7 @@
         <v>45315</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9590,7 +9590,7 @@
         <v>44903</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9668,7 +9668,7 @@
         <v>45314</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9741,7 +9741,7 @@
         <v>45306</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9814,7 +9814,7 @@
         <v>45142</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9887,7 +9887,7 @@
         <v>46017</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9960,7 +9960,7 @@
         <v>45734</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10038,7 +10038,7 @@
         <v>45884</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10116,7 +10116,7 @@
         <v>45159</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10189,7 +10189,7 @@
         <v>45796</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10262,7 +10262,7 @@
         <v>44938</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10335,7 +10335,7 @@
         <v>45334</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10408,7 +10408,7 @@
         <v>45531</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10481,7 +10481,7 @@
         <v>45315</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10554,7 +10554,7 @@
         <v>45888</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10632,7 +10632,7 @@
         <v>45853</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10705,7 +10705,7 @@
         <v>45756</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10778,7 +10778,7 @@
         <v>45635</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10851,7 +10851,7 @@
         <v>45889</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10924,7 +10924,7 @@
         <v>45889</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10997,7 +10997,7 @@
         <v>46036</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11070,7 +11070,7 @@
         <v>45799</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11148,7 +11148,7 @@
         <v>45709</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11221,7 +11221,7 @@
         <v>45800</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11299,7 +11299,7 @@
         <v>45721</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11372,7 +11372,7 @@
         <v>45586</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11445,7 +11445,7 @@
         <v>45586</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11518,7 +11518,7 @@
         <v>45800</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11591,7 +11591,7 @@
         <v>45799</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11669,7 +11669,7 @@
         <v>46052</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11742,7 +11742,7 @@
         <v>46051</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11815,7 +11815,7 @@
         <v>45670</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11888,7 +11888,7 @@
         <v>45803</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11961,7 +11961,7 @@
         <v>45547</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12034,7 +12034,7 @@
         <v>46009</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12112,7 +12112,7 @@
         <v>46010</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12190,7 +12190,7 @@
         <v>46009</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12268,7 +12268,7 @@
         <v>46010</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12346,7 +12346,7 @@
         <v>46062</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12419,7 +12419,7 @@
         <v>45992</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12492,7 +12492,7 @@
         <v>46062</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12565,7 +12565,7 @@
         <v>44938</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12638,7 +12638,7 @@
         <v>45401</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12711,7 +12711,7 @@
         <v>44599</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12789,7 +12789,7 @@
         <v>45929</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12862,7 +12862,7 @@
         <v>45905</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12935,7 +12935,7 @@
         <v>45932</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13008,7 +13008,7 @@
         <v>45810</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13081,7 +13081,7 @@
         <v>45810</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13154,7 +13154,7 @@
         <v>45439</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13227,7 +13227,7 @@
         <v>46091</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13300,7 +13300,7 @@
         <v>45937</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13373,7 +13373,7 @@
         <v>45810</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13446,7 +13446,7 @@
         <v>46099</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13519,7 +13519,7 @@
         <v>44750</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13597,7 +13597,7 @@
         <v>45590</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13670,7 +13670,7 @@
         <v>45947</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13743,7 +13743,7 @@
         <v>45947</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13816,7 +13816,7 @@
         <v>45947</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13889,7 +13889,7 @@
         <v>45953</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13967,7 +13967,7 @@
         <v>45958</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14040,7 +14040,7 @@
         <v>45594</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14113,7 +14113,7 @@
         <v>44825</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14186,7 +14186,7 @@
         <v>45076</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14259,7 +14259,7 @@
         <v>45699</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14337,7 +14337,7 @@
         <v>45006</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14410,7 +14410,7 @@
         <v>45161</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14483,7 +14483,7 @@
         <v>45002</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14556,7 +14556,7 @@
         <v>45894</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14629,7 +14629,7 @@
         <v>45847</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14702,7 +14702,7 @@
         <v>45590</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14775,7 +14775,7 @@
         <v>45989</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14853,7 +14853,7 @@
         <v>45989</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14931,7 +14931,7 @@
         <v>45693</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15004,7 +15004,7 @@
         <v>46001</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15077,7 +15077,7 @@
         <v>46002</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15150,7 +15150,7 @@
         <v>46002</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15223,7 +15223,7 @@
         <v>46001</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15296,7 +15296,7 @@
         <v>46001</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15369,7 +15369,7 @@
         <v>44820</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15442,7 +15442,7 @@
         <v>46008</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15515,7 +15515,7 @@
         <v>46008</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15588,7 +15588,7 @@
         <v>45201</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15661,7 +15661,7 @@
         <v>46013</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15734,7 +15734,7 @@
         <v>45824</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15812,7 +15812,7 @@
         <v>45821</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15885,7 +15885,7 @@
         <v>45821</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15958,7 +15958,7 @@
         <v>45376</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16031,7 +16031,7 @@
         <v>45821</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16104,7 +16104,7 @@
         <v>45821</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16177,7 +16177,7 @@
         <v>45685</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16250,7 +16250,7 @@
         <v>45827</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16328,7 +16328,7 @@
         <v>44739</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16401,7 +16401,7 @@
         <v>45706</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16474,7 +16474,7 @@
         <v>45721</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16547,7 +16547,7 @@
         <v>46149</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16620,7 +16620,7 @@
         <v>45259</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16693,7 +16693,7 @@
         <v>46139</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16766,7 +16766,7 @@
         <v>44804</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16839,7 +16839,7 @@
         <v>45267</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16912,7 +16912,7 @@
         <v>45842</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16985,7 +16985,7 @@
         <v>45846</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17058,7 +17058,7 @@
         <v>45846</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17131,7 +17131,7 @@
         <v>45846</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17204,7 +17204,7 @@
         <v>46038</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17277,7 +17277,7 @@
         <v>45093</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17350,7 +17350,7 @@
         <v>45769</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17423,7 +17423,7 @@
         <v>46174</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17496,7 +17496,7 @@
         <v>44959</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17569,7 +17569,7 @@
         <v>45418</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17642,7 +17642,7 @@
         <v>45693</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17715,7 +17715,7 @@
         <v>45306</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17788,7 +17788,7 @@
         <v>46182</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17861,7 +17861,7 @@
         <v>46182</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17934,7 +17934,7 @@
         <v>46185</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18007,7 +18007,7 @@
         <v>45539</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -18080,7 +18080,7 @@
         <v>45169</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -18153,7 +18153,7 @@
         <v>45560</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -18226,7 +18226,7 @@
         <v>46202</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18299,7 +18299,7 @@
         <v>45590</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18372,7 +18372,7 @@
         <v>45230</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18445,7 +18445,7 @@
         <v>46253</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18518,7 +18518,7 @@
         <v>45163</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18591,7 +18591,7 @@
         <v>46129</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18664,7 +18664,7 @@
         <v>45385</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18737,7 +18737,7 @@
         <v>45204</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18810,7 +18810,7 @@
         <v>45749</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18888,7 +18888,7 @@
         <v>44811</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18961,7 +18961,7 @@
         <v>45134</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19034,7 +19034,7 @@
         <v>45694</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -19107,7 +19107,7 @@
         <v>46272</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -19180,7 +19180,7 @@
         <v>46269</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -19253,7 +19253,7 @@
         <v>45211</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19326,7 +19326,7 @@
         <v>44586</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19399,7 +19399,7 @@
         <v>45301</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19472,7 +19472,7 @@
         <v>44796</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19545,7 +19545,7 @@
         <v>44636</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19618,7 +19618,7 @@
         <v>45737</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19691,7 +19691,7 @@
         <v>46283</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19764,7 +19764,7 @@
         <v>45636</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19837,7 +19837,7 @@
         <v>44601</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19915,7 +19915,7 @@
         <v>44963</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19988,7 +19988,7 @@
         <v>44600</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20061,7 +20061,7 @@
         <v>46288</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -20134,7 +20134,7 @@
         <v>45013</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -20207,7 +20207,7 @@
         <v>44523</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20285,7 +20285,7 @@
         <v>45105</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20358,7 +20358,7 @@
         <v>45324</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20431,7 +20431,7 @@
         <v>45086</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20504,7 +20504,7 @@
         <v>44495</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20577,7 +20577,7 @@
         <v>45530</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20650,7 +20650,7 @@
         <v>45210</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20723,7 +20723,7 @@
         <v>45320</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20796,7 +20796,7 @@
         <v>45197</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20869,7 +20869,7 @@
         <v>45687</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20942,7 +20942,7 @@
         <v>45215</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -21015,7 +21015,7 @@
         <v>44743</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -21088,7 +21088,7 @@
         <v>45706</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -21161,7 +21161,7 @@
         <v>45082</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -21234,7 +21234,7 @@
         <v>45742</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -21307,7 +21307,7 @@
         <v>45093</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -21380,7 +21380,7 @@
         <v>45259</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21453,7 +21453,7 @@
         <v>45775</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21526,7 +21526,7 @@
         <v>45792</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21599,7 +21599,7 @@
         <v>45710</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21672,7 +21672,7 @@
         <v>45743</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21745,7 +21745,7 @@
         <v>45715</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21818,7 +21818,7 @@
         <v>44986</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21916,7 +21916,7 @@
         <v>45716</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>

--- a/Översikt SKÖVDE.xlsx
+++ b/Översikt SKÖVDE.xlsx
@@ -601,7 +601,7 @@
         <v>46196</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -736,7 +736,7 @@
         <v>46198</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -852,7 +852,7 @@
         <v>45876</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -966,7 +966,7 @@
         <v>45743</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1080,7 +1080,7 @@
         <v>46182</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1190,7 +1190,7 @@
         <v>44495</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1300,7 +1300,7 @@
         <v>45201</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1409,7 +1409,7 @@
         <v>46080</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1518,7 +1518,7 @@
         <v>46014</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1627,7 +1627,7 @@
         <v>44595</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1744,7 +1744,7 @@
         <v>44594</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1861,7 +1861,7 @@
         <v>45306</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1977,7 +1977,7 @@
         <v>44949</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2094,7 +2094,7 @@
         <v>45979</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2206,7 +2206,7 @@
         <v>45714</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2323,7 +2323,7 @@
         <v>45387</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2431,7 +2431,7 @@
         <v>44837</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2538,7 +2538,7 @@
         <v>44804</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2650,7 +2650,7 @@
         <v>45506</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2757,7 +2757,7 @@
         <v>45824</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2869,7 +2869,7 @@
         <v>45334</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2980,7 +2980,7 @@
         <v>45334</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3091,7 +3091,7 @@
         <v>44943</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3198,7 +3198,7 @@
         <v>44817</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3305,7 +3305,7 @@
         <v>46289</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3412,7 +3412,7 @@
         <v>44928</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3524,7 +3524,7 @@
         <v>45800</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3635,7 +3635,7 @@
         <v>45471</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3741,7 +3741,7 @@
         <v>45972</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3847,7 +3847,7 @@
         <v>44495</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3953,7 +3953,7 @@
         <v>45799</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4064,7 +4064,7 @@
         <v>45797</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4179,7 +4179,7 @@
         <v>44988</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4290,7 +4290,7 @@
         <v>46185</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4396,7 +4396,7 @@
         <v>45903</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4507,7 +4507,7 @@
         <v>44750</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4618,7 +4618,7 @@
         <v>45635</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4724,7 +4724,7 @@
         <v>45785</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4834,7 +4834,7 @@
         <v>45743</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4940,7 +4940,7 @@
         <v>44834</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5050,7 +5050,7 @@
         <v>44475</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5155,7 +5155,7 @@
         <v>46045</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5260,7 +5260,7 @@
         <v>46052</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5365,7 +5365,7 @@
         <v>45810</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5475,7 +5475,7 @@
         <v>45932</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5580,7 +5580,7 @@
         <v>45645</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5685,7 +5685,7 @@
         <v>45322</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5790,7 +5790,7 @@
         <v>45755</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5900,7 +5900,7 @@
         <v>46198</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6005,7 +6005,7 @@
         <v>45104</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6115,7 +6115,7 @@
         <v>45019</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6220,7 +6220,7 @@
         <v>44988</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6325,7 +6325,7 @@
         <v>45204</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6430,7 +6430,7 @@
         <v>46173</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6535,7 +6535,7 @@
         <v>45224</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6640,7 +6640,7 @@
         <v>46272</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6745,7 +6745,7 @@
         <v>45036</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6850,7 +6850,7 @@
         <v>45040</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6955,7 +6955,7 @@
         <v>45148</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7060,7 +7060,7 @@
         <v>45182</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7170,7 +7170,7 @@
         <v>45322</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7275,7 +7275,7 @@
         <v>44986</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7385,7 +7385,7 @@
         <v>44594</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7463,7 +7463,7 @@
         <v>44609</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7536,7 +7536,7 @@
         <v>44543</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7614,7 +7614,7 @@
         <v>44516</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7687,7 +7687,7 @@
         <v>44844</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7760,7 +7760,7 @@
         <v>44567</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7833,7 +7833,7 @@
         <v>44523</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7906,7 +7906,7 @@
         <v>44748</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7979,7 +7979,7 @@
         <v>44748</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8052,7 +8052,7 @@
         <v>44585</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8125,7 +8125,7 @@
         <v>44614</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8203,7 +8203,7 @@
         <v>44698</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8276,7 +8276,7 @@
         <v>44740</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8349,7 +8349,7 @@
         <v>44530</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8422,7 +8422,7 @@
         <v>44698</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8495,7 +8495,7 @@
         <v>44847</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8568,7 +8568,7 @@
         <v>44635</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8641,7 +8641,7 @@
         <v>44823</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8714,7 +8714,7 @@
         <v>44629</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8787,7 +8787,7 @@
         <v>44481</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8860,7 +8860,7 @@
         <v>44762</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8933,7 +8933,7 @@
         <v>44809</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9006,7 +9006,7 @@
         <v>45267</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9079,7 +9079,7 @@
         <v>45322</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9152,7 +9152,7 @@
         <v>44862</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9225,7 +9225,7 @@
         <v>45138</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9298,7 +9298,7 @@
         <v>45299</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9371,7 +9371,7 @@
         <v>45301</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9444,7 +9444,7 @@
         <v>45245</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9517,7 +9517,7 @@
         <v>45315</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9590,7 +9590,7 @@
         <v>44903</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9668,7 +9668,7 @@
         <v>45314</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9741,7 +9741,7 @@
         <v>45306</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9814,7 +9814,7 @@
         <v>45142</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9887,7 +9887,7 @@
         <v>46017</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9960,7 +9960,7 @@
         <v>45734</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10038,7 +10038,7 @@
         <v>45884</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10116,7 +10116,7 @@
         <v>45159</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10189,7 +10189,7 @@
         <v>45796</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10262,7 +10262,7 @@
         <v>44938</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10335,7 +10335,7 @@
         <v>45334</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10408,7 +10408,7 @@
         <v>45531</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10481,7 +10481,7 @@
         <v>45315</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10554,7 +10554,7 @@
         <v>45888</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10632,7 +10632,7 @@
         <v>45853</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10705,7 +10705,7 @@
         <v>45756</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10778,7 +10778,7 @@
         <v>45635</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10851,7 +10851,7 @@
         <v>45889</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10924,7 +10924,7 @@
         <v>45889</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10997,7 +10997,7 @@
         <v>46036</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11070,7 +11070,7 @@
         <v>45799</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11148,7 +11148,7 @@
         <v>45709</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11221,7 +11221,7 @@
         <v>45800</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11299,7 +11299,7 @@
         <v>45721</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11372,7 +11372,7 @@
         <v>45586</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11445,7 +11445,7 @@
         <v>45586</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11518,7 +11518,7 @@
         <v>45800</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11591,7 +11591,7 @@
         <v>45799</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11669,7 +11669,7 @@
         <v>46052</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11742,7 +11742,7 @@
         <v>46051</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11815,7 +11815,7 @@
         <v>45670</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11888,7 +11888,7 @@
         <v>45803</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11961,7 +11961,7 @@
         <v>45547</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12034,7 +12034,7 @@
         <v>46009</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12112,7 +12112,7 @@
         <v>46010</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12190,7 +12190,7 @@
         <v>46009</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12268,7 +12268,7 @@
         <v>46010</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12346,7 +12346,7 @@
         <v>46062</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12419,7 +12419,7 @@
         <v>45992</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12492,7 +12492,7 @@
         <v>46062</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12565,7 +12565,7 @@
         <v>44938</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12638,7 +12638,7 @@
         <v>45401</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12711,7 +12711,7 @@
         <v>44599</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12789,7 +12789,7 @@
         <v>45929</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12862,7 +12862,7 @@
         <v>45905</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12935,7 +12935,7 @@
         <v>45932</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13008,7 +13008,7 @@
         <v>45810</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13081,7 +13081,7 @@
         <v>45810</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13154,7 +13154,7 @@
         <v>45439</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13227,7 +13227,7 @@
         <v>46091</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13300,7 +13300,7 @@
         <v>45937</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13373,7 +13373,7 @@
         <v>45810</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13446,7 +13446,7 @@
         <v>46099</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13519,7 +13519,7 @@
         <v>44750</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13597,7 +13597,7 @@
         <v>45590</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13670,7 +13670,7 @@
         <v>45947</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13743,7 +13743,7 @@
         <v>45947</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13816,7 +13816,7 @@
         <v>45947</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13889,7 +13889,7 @@
         <v>45953</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13967,7 +13967,7 @@
         <v>45958</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14040,7 +14040,7 @@
         <v>45594</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14113,7 +14113,7 @@
         <v>44825</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14186,7 +14186,7 @@
         <v>45076</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14259,7 +14259,7 @@
         <v>45699</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14337,7 +14337,7 @@
         <v>45006</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14410,7 +14410,7 @@
         <v>45161</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14483,7 +14483,7 @@
         <v>45002</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14556,7 +14556,7 @@
         <v>45894</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14629,7 +14629,7 @@
         <v>45847</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14702,7 +14702,7 @@
         <v>45590</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14775,7 +14775,7 @@
         <v>45989</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14853,7 +14853,7 @@
         <v>45989</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14931,7 +14931,7 @@
         <v>45693</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15004,7 +15004,7 @@
         <v>46001</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15077,7 +15077,7 @@
         <v>46002</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15150,7 +15150,7 @@
         <v>46002</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15223,7 +15223,7 @@
         <v>46001</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15296,7 +15296,7 @@
         <v>46001</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15369,7 +15369,7 @@
         <v>44820</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15442,7 +15442,7 @@
         <v>46008</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15515,7 +15515,7 @@
         <v>46008</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15588,7 +15588,7 @@
         <v>45201</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15661,7 +15661,7 @@
         <v>46013</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15734,7 +15734,7 @@
         <v>45824</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15812,7 +15812,7 @@
         <v>45821</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15885,7 +15885,7 @@
         <v>45821</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15958,7 +15958,7 @@
         <v>45376</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16031,7 +16031,7 @@
         <v>45821</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16104,7 +16104,7 @@
         <v>45821</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16177,7 +16177,7 @@
         <v>45685</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16250,7 +16250,7 @@
         <v>45827</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16328,7 +16328,7 @@
         <v>44739</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16401,7 +16401,7 @@
         <v>45706</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16474,7 +16474,7 @@
         <v>45721</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16547,7 +16547,7 @@
         <v>46149</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16620,7 +16620,7 @@
         <v>45259</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16693,7 +16693,7 @@
         <v>46139</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16766,7 +16766,7 @@
         <v>44804</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16839,7 +16839,7 @@
         <v>45267</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16912,7 +16912,7 @@
         <v>45842</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16985,7 +16985,7 @@
         <v>45846</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17058,7 +17058,7 @@
         <v>45846</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17131,7 +17131,7 @@
         <v>45846</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17204,7 +17204,7 @@
         <v>46038</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17277,7 +17277,7 @@
         <v>45093</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17350,7 +17350,7 @@
         <v>45769</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17423,7 +17423,7 @@
         <v>46174</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17496,7 +17496,7 @@
         <v>44959</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17569,7 +17569,7 @@
         <v>45418</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17642,7 +17642,7 @@
         <v>45693</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17715,7 +17715,7 @@
         <v>45306</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17788,7 +17788,7 @@
         <v>46182</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17861,7 +17861,7 @@
         <v>46182</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17934,7 +17934,7 @@
         <v>46185</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18007,7 +18007,7 @@
         <v>45539</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -18080,7 +18080,7 @@
         <v>45169</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -18153,7 +18153,7 @@
         <v>45560</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -18226,7 +18226,7 @@
         <v>46202</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18299,7 +18299,7 @@
         <v>45590</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18372,7 +18372,7 @@
         <v>45230</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18445,7 +18445,7 @@
         <v>46253</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18518,7 +18518,7 @@
         <v>45163</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18591,7 +18591,7 @@
         <v>46129</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18664,7 +18664,7 @@
         <v>45385</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18737,7 +18737,7 @@
         <v>45204</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18810,7 +18810,7 @@
         <v>45749</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18888,7 +18888,7 @@
         <v>44811</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18961,7 +18961,7 @@
         <v>45134</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19034,7 +19034,7 @@
         <v>45694</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -19107,7 +19107,7 @@
         <v>46272</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -19180,7 +19180,7 @@
         <v>46269</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -19253,7 +19253,7 @@
         <v>45211</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19326,7 +19326,7 @@
         <v>44586</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19399,7 +19399,7 @@
         <v>45301</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19472,7 +19472,7 @@
         <v>44796</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19545,7 +19545,7 @@
         <v>44636</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19618,7 +19618,7 @@
         <v>45737</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19691,7 +19691,7 @@
         <v>46283</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19764,7 +19764,7 @@
         <v>45636</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19837,7 +19837,7 @@
         <v>44601</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19915,7 +19915,7 @@
         <v>44963</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19988,7 +19988,7 @@
         <v>44600</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20061,7 +20061,7 @@
         <v>46288</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -20134,7 +20134,7 @@
         <v>45013</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -20207,7 +20207,7 @@
         <v>44523</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20285,7 +20285,7 @@
         <v>45105</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20358,7 +20358,7 @@
         <v>45324</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20431,7 +20431,7 @@
         <v>45086</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20504,7 +20504,7 @@
         <v>44495</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20577,7 +20577,7 @@
         <v>45530</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20650,7 +20650,7 @@
         <v>45210</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20723,7 +20723,7 @@
         <v>45320</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20796,7 +20796,7 @@
         <v>45197</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20869,7 +20869,7 @@
         <v>45687</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20942,7 +20942,7 @@
         <v>45215</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -21015,7 +21015,7 @@
         <v>44743</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -21088,7 +21088,7 @@
         <v>45706</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -21161,7 +21161,7 @@
         <v>45082</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -21234,7 +21234,7 @@
         <v>45742</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -21307,7 +21307,7 @@
         <v>45093</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -21380,7 +21380,7 @@
         <v>45259</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21453,7 +21453,7 @@
         <v>45775</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21526,7 +21526,7 @@
         <v>45792</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21599,7 +21599,7 @@
         <v>45710</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21672,7 +21672,7 @@
         <v>45743</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21745,7 +21745,7 @@
         <v>45715</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21818,7 +21818,7 @@
         <v>44986</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21916,7 +21916,7 @@
         <v>45716</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>

--- a/Översikt SKÖVDE.xlsx
+++ b/Översikt SKÖVDE.xlsx
@@ -601,7 +601,7 @@
         <v>46196</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -736,7 +736,7 @@
         <v>46198</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -852,7 +852,7 @@
         <v>45876</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -966,7 +966,7 @@
         <v>45743</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1080,7 +1080,7 @@
         <v>46182</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1190,7 +1190,7 @@
         <v>44495</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1300,7 +1300,7 @@
         <v>46014</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1409,7 +1409,7 @@
         <v>46080</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1518,7 +1518,7 @@
         <v>45201</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1627,7 +1627,7 @@
         <v>44595</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1744,7 +1744,7 @@
         <v>44594</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1861,7 +1861,7 @@
         <v>45979</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1973,7 +1973,7 @@
         <v>45714</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2090,7 +2090,7 @@
         <v>45306</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2206,7 +2206,7 @@
         <v>44949</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2323,7 +2323,7 @@
         <v>45387</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2431,7 +2431,7 @@
         <v>45506</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2538,7 +2538,7 @@
         <v>45824</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2650,7 +2650,7 @@
         <v>44928</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2762,7 +2762,7 @@
         <v>45334</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2873,7 +2873,7 @@
         <v>45334</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2984,7 +2984,7 @@
         <v>44943</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3091,7 +3091,7 @@
         <v>44804</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3203,7 +3203,7 @@
         <v>46289</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3310,7 +3310,7 @@
         <v>44817</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3417,7 +3417,7 @@
         <v>44837</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3524,7 +3524,7 @@
         <v>45743</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3630,7 +3630,7 @@
         <v>45471</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3736,7 +3736,7 @@
         <v>45800</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3847,7 +3847,7 @@
         <v>45972</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3953,7 +3953,7 @@
         <v>45799</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4064,7 +4064,7 @@
         <v>45635</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4170,7 +4170,7 @@
         <v>45797</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4285,7 +4285,7 @@
         <v>46185</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4391,7 +4391,7 @@
         <v>44988</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4502,7 +4502,7 @@
         <v>45903</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4613,7 +4613,7 @@
         <v>44495</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4719,7 +4719,7 @@
         <v>44750</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4830,7 +4830,7 @@
         <v>45785</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4940,7 +4940,7 @@
         <v>44834</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5050,7 +5050,7 @@
         <v>44475</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5155,7 +5155,7 @@
         <v>44988</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5260,7 +5260,7 @@
         <v>45148</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5365,7 +5365,7 @@
         <v>45755</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5475,7 +5475,7 @@
         <v>46045</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5580,7 +5580,7 @@
         <v>45810</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5690,7 +5690,7 @@
         <v>46052</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5795,7 +5795,7 @@
         <v>45932</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5900,7 +5900,7 @@
         <v>45322</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6005,7 +6005,7 @@
         <v>46198</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6110,7 +6110,7 @@
         <v>45204</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6215,7 +6215,7 @@
         <v>45645</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6320,7 +6320,7 @@
         <v>45182</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6430,7 +6430,7 @@
         <v>45224</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6535,7 +6535,7 @@
         <v>46173</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6640,7 +6640,7 @@
         <v>46272</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6745,7 +6745,7 @@
         <v>45104</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6855,7 +6855,7 @@
         <v>45019</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6960,7 +6960,7 @@
         <v>45040</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7065,7 +7065,7 @@
         <v>45036</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7170,7 +7170,7 @@
         <v>45322</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7275,7 +7275,7 @@
         <v>44986</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7385,7 +7385,7 @@
         <v>44594</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7463,7 +7463,7 @@
         <v>44609</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7536,7 +7536,7 @@
         <v>44543</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7614,7 +7614,7 @@
         <v>44516</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7687,7 +7687,7 @@
         <v>44844</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7760,7 +7760,7 @@
         <v>44567</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7833,7 +7833,7 @@
         <v>44523</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7906,7 +7906,7 @@
         <v>44748</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7979,7 +7979,7 @@
         <v>44748</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8052,7 +8052,7 @@
         <v>44585</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8125,7 +8125,7 @@
         <v>44614</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8203,7 +8203,7 @@
         <v>44698</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8276,7 +8276,7 @@
         <v>44740</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8349,7 +8349,7 @@
         <v>44530</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8422,7 +8422,7 @@
         <v>44698</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8495,7 +8495,7 @@
         <v>44847</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8568,7 +8568,7 @@
         <v>44635</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8641,7 +8641,7 @@
         <v>44481</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8714,7 +8714,7 @@
         <v>44823</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8787,7 +8787,7 @@
         <v>44629</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8860,7 +8860,7 @@
         <v>44762</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8933,7 +8933,7 @@
         <v>44809</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9006,7 +9006,7 @@
         <v>44743</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9079,7 +9079,7 @@
         <v>44959</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9152,7 +9152,7 @@
         <v>45201</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9225,7 +9225,7 @@
         <v>45197</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9298,7 +9298,7 @@
         <v>45322</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9371,7 +9371,7 @@
         <v>45756</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9444,7 +9444,7 @@
         <v>46002</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9517,7 +9517,7 @@
         <v>46002</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9590,7 +9590,7 @@
         <v>45539</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9663,7 +9663,7 @@
         <v>46008</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9736,7 +9736,7 @@
         <v>46008</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9809,7 +9809,7 @@
         <v>45715</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9882,7 +9882,7 @@
         <v>45884</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9960,7 +9960,7 @@
         <v>45749</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10038,7 +10038,7 @@
         <v>45721</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10111,7 +10111,7 @@
         <v>44903</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10189,7 +10189,7 @@
         <v>46013</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10262,7 +10262,7 @@
         <v>45853</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10335,7 +10335,7 @@
         <v>44601</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10413,7 +10413,7 @@
         <v>45888</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10491,7 +10491,7 @@
         <v>45889</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10564,7 +10564,7 @@
         <v>45889</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10637,7 +10637,7 @@
         <v>45635</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10710,7 +10710,7 @@
         <v>46017</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10783,7 +10783,7 @@
         <v>45709</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10856,7 +10856,7 @@
         <v>45230</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10929,7 +10929,7 @@
         <v>45743</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11002,7 +11002,7 @@
         <v>45710</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11075,7 +11075,7 @@
         <v>45093</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11148,7 +11148,7 @@
         <v>45792</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11221,7 +11221,7 @@
         <v>45163</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11294,7 +11294,7 @@
         <v>46036</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11367,7 +11367,7 @@
         <v>45334</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11440,7 +11440,7 @@
         <v>45142</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11513,7 +11513,7 @@
         <v>45734</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11591,7 +11591,7 @@
         <v>45215</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11664,7 +11664,7 @@
         <v>45796</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11737,7 +11737,7 @@
         <v>45799</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11815,7 +11815,7 @@
         <v>45799</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11893,7 +11893,7 @@
         <v>45803</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11966,7 +11966,7 @@
         <v>46051</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12039,7 +12039,7 @@
         <v>45800</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12117,7 +12117,7 @@
         <v>45800</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12190,7 +12190,7 @@
         <v>46052</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12263,7 +12263,7 @@
         <v>45161</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12336,7 +12336,7 @@
         <v>45929</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12409,7 +12409,7 @@
         <v>45699</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12487,7 +12487,7 @@
         <v>45992</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12560,7 +12560,7 @@
         <v>46010</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12638,7 +12638,7 @@
         <v>45905</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12711,7 +12711,7 @@
         <v>46062</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12784,7 +12784,7 @@
         <v>46010</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12862,7 +12862,7 @@
         <v>45439</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12935,7 +12935,7 @@
         <v>46009</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13013,7 +13013,7 @@
         <v>46009</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13091,7 +13091,7 @@
         <v>46062</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13164,7 +13164,7 @@
         <v>45932</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13237,7 +13237,7 @@
         <v>44523</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13315,7 +13315,7 @@
         <v>45385</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13388,7 +13388,7 @@
         <v>45937</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13461,7 +13461,7 @@
         <v>45810</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13534,7 +13534,7 @@
         <v>45810</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13607,7 +13607,7 @@
         <v>45947</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13680,7 +13680,7 @@
         <v>45947</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13753,7 +13753,7 @@
         <v>45810</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13826,7 +13826,7 @@
         <v>45947</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13899,7 +13899,7 @@
         <v>45953</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13977,7 +13977,7 @@
         <v>45958</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14050,7 +14050,7 @@
         <v>46091</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14123,7 +14123,7 @@
         <v>44862</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14196,7 +14196,7 @@
         <v>46099</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14269,7 +14269,7 @@
         <v>45259</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14342,7 +14342,7 @@
         <v>45594</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14415,7 +14415,7 @@
         <v>45821</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14488,7 +14488,7 @@
         <v>45821</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14561,7 +14561,7 @@
         <v>45824</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14639,7 +14639,7 @@
         <v>45267</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14712,7 +14712,7 @@
         <v>45989</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14790,7 +14790,7 @@
         <v>45989</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14868,7 +14868,7 @@
         <v>45821</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14941,7 +14941,7 @@
         <v>45821</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15014,7 +15014,7 @@
         <v>45827</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15092,7 +15092,7 @@
         <v>45670</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15165,7 +15165,7 @@
         <v>46001</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15238,7 +15238,7 @@
         <v>46001</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15311,7 +15311,7 @@
         <v>46001</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15384,7 +15384,7 @@
         <v>45301</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15457,7 +15457,7 @@
         <v>45204</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15530,7 +15530,7 @@
         <v>45894</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15603,7 +15603,7 @@
         <v>45685</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15676,7 +15676,7 @@
         <v>45847</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15749,7 +15749,7 @@
         <v>45211</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15822,7 +15822,7 @@
         <v>44586</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15895,7 +15895,7 @@
         <v>45693</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15968,7 +15968,7 @@
         <v>45842</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16041,7 +16041,7 @@
         <v>45846</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16114,7 +16114,7 @@
         <v>45846</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16187,7 +16187,7 @@
         <v>45846</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16260,7 +16260,7 @@
         <v>45530</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16333,7 +16333,7 @@
         <v>45401</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16406,7 +16406,7 @@
         <v>44963</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16479,7 +16479,7 @@
         <v>45376</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16552,7 +16552,7 @@
         <v>44938</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16625,7 +16625,7 @@
         <v>45769</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16698,7 +16698,7 @@
         <v>45320</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16771,7 +16771,7 @@
         <v>44495</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16844,7 +16844,7 @@
         <v>44600</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16917,7 +16917,7 @@
         <v>44739</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16990,7 +16990,7 @@
         <v>45560</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17063,7 +17063,7 @@
         <v>45693</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17136,7 +17136,7 @@
         <v>45306</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17209,7 +17209,7 @@
         <v>46149</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17282,7 +17282,7 @@
         <v>45531</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17355,7 +17355,7 @@
         <v>45324</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17428,7 +17428,7 @@
         <v>45245</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17501,7 +17501,7 @@
         <v>45636</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17574,7 +17574,7 @@
         <v>45694</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17647,7 +17647,7 @@
         <v>46139</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17720,7 +17720,7 @@
         <v>45267</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17793,7 +17793,7 @@
         <v>46038</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17866,7 +17866,7 @@
         <v>45315</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17939,7 +17939,7 @@
         <v>45013</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18012,7 +18012,7 @@
         <v>46174</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -18085,7 +18085,7 @@
         <v>45586</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -18158,7 +18158,7 @@
         <v>45086</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -18231,7 +18231,7 @@
         <v>45006</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18304,7 +18304,7 @@
         <v>46182</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18377,7 +18377,7 @@
         <v>46182</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18450,7 +18450,7 @@
         <v>46185</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18523,7 +18523,7 @@
         <v>44796</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18596,7 +18596,7 @@
         <v>45076</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18669,7 +18669,7 @@
         <v>45742</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18742,7 +18742,7 @@
         <v>46202</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18815,7 +18815,7 @@
         <v>44599</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18893,7 +18893,7 @@
         <v>44750</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18971,7 +18971,7 @@
         <v>44636</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19044,7 +19044,7 @@
         <v>45105</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -19117,7 +19117,7 @@
         <v>45314</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -19190,7 +19190,7 @@
         <v>45259</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -19263,7 +19263,7 @@
         <v>46129</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19336,7 +19336,7 @@
         <v>44938</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19409,7 +19409,7 @@
         <v>46269</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19482,7 +19482,7 @@
         <v>46272</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19555,7 +19555,7 @@
         <v>44820</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19628,7 +19628,7 @@
         <v>45299</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19701,7 +19701,7 @@
         <v>45169</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19774,7 +19774,7 @@
         <v>45093</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19847,7 +19847,7 @@
         <v>45590</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19920,7 +19920,7 @@
         <v>45586</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19993,7 +19993,7 @@
         <v>46283</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20066,7 +20066,7 @@
         <v>45082</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -20139,7 +20139,7 @@
         <v>45687</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -20212,7 +20212,7 @@
         <v>45138</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20285,7 +20285,7 @@
         <v>46288</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20358,7 +20358,7 @@
         <v>45134</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20431,7 +20431,7 @@
         <v>46293</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20504,7 +20504,7 @@
         <v>45590</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20577,7 +20577,7 @@
         <v>45418</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20650,7 +20650,7 @@
         <v>45301</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20723,7 +20723,7 @@
         <v>46253</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20796,7 +20796,7 @@
         <v>44811</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20869,7 +20869,7 @@
         <v>45706</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20942,7 +20942,7 @@
         <v>45210</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -21015,7 +21015,7 @@
         <v>45002</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -21088,7 +21088,7 @@
         <v>45706</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -21161,7 +21161,7 @@
         <v>44825</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -21234,7 +21234,7 @@
         <v>45590</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -21307,7 +21307,7 @@
         <v>44804</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -21380,7 +21380,7 @@
         <v>45159</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21453,7 +21453,7 @@
         <v>45306</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21526,7 +21526,7 @@
         <v>45721</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21599,7 +21599,7 @@
         <v>45315</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21672,7 +21672,7 @@
         <v>45737</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21745,7 +21745,7 @@
         <v>45547</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21818,7 +21818,7 @@
         <v>45775</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21891,7 +21891,7 @@
         <v>44986</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21989,7 +21989,7 @@
         <v>45716</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>

--- a/Översikt SKÖVDE.xlsx
+++ b/Översikt SKÖVDE.xlsx
@@ -601,7 +601,7 @@
         <v>46196</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -736,7 +736,7 @@
         <v>46198</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -852,7 +852,7 @@
         <v>45876</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -966,7 +966,7 @@
         <v>45743</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1080,7 +1080,7 @@
         <v>46182</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1190,7 +1190,7 @@
         <v>44495</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1300,7 +1300,7 @@
         <v>46014</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1409,7 +1409,7 @@
         <v>46080</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1518,7 +1518,7 @@
         <v>45201</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1627,7 +1627,7 @@
         <v>44595</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1744,7 +1744,7 @@
         <v>44594</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1861,7 +1861,7 @@
         <v>45979</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1973,7 +1973,7 @@
         <v>45714</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2090,7 +2090,7 @@
         <v>45306</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2206,7 +2206,7 @@
         <v>44949</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2323,7 +2323,7 @@
         <v>45387</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2431,7 +2431,7 @@
         <v>45506</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2538,7 +2538,7 @@
         <v>45824</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2650,7 +2650,7 @@
         <v>44928</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2762,7 +2762,7 @@
         <v>45334</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2873,7 +2873,7 @@
         <v>45334</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2984,7 +2984,7 @@
         <v>44943</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3091,7 +3091,7 @@
         <v>44804</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3203,7 +3203,7 @@
         <v>46289</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3310,7 +3310,7 @@
         <v>44817</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3417,7 +3417,7 @@
         <v>44837</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3524,7 +3524,7 @@
         <v>45743</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3630,7 +3630,7 @@
         <v>45471</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3736,7 +3736,7 @@
         <v>45800</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3847,7 +3847,7 @@
         <v>45972</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3953,7 +3953,7 @@
         <v>45799</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4064,7 +4064,7 @@
         <v>45635</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4170,7 +4170,7 @@
         <v>45797</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4285,7 +4285,7 @@
         <v>46185</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4391,7 +4391,7 @@
         <v>44988</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4502,7 +4502,7 @@
         <v>45903</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4613,7 +4613,7 @@
         <v>44495</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4719,7 +4719,7 @@
         <v>44750</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4830,7 +4830,7 @@
         <v>45785</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4940,7 +4940,7 @@
         <v>44834</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5050,7 +5050,7 @@
         <v>44475</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5155,7 +5155,7 @@
         <v>44988</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5260,7 +5260,7 @@
         <v>45148</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5365,7 +5365,7 @@
         <v>45755</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5475,7 +5475,7 @@
         <v>46045</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5580,7 +5580,7 @@
         <v>45810</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5690,7 +5690,7 @@
         <v>46052</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5795,7 +5795,7 @@
         <v>45932</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5900,7 +5900,7 @@
         <v>45322</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6005,7 +6005,7 @@
         <v>46198</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6110,7 +6110,7 @@
         <v>45204</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6215,7 +6215,7 @@
         <v>45645</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6320,7 +6320,7 @@
         <v>45182</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6430,7 +6430,7 @@
         <v>45224</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6535,7 +6535,7 @@
         <v>46173</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6640,7 +6640,7 @@
         <v>46272</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6745,7 +6745,7 @@
         <v>45104</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6855,7 +6855,7 @@
         <v>45019</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6960,7 +6960,7 @@
         <v>45040</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7065,7 +7065,7 @@
         <v>45036</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7170,7 +7170,7 @@
         <v>45322</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7275,7 +7275,7 @@
         <v>44986</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7385,7 +7385,7 @@
         <v>44594</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7463,7 +7463,7 @@
         <v>44609</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7536,7 +7536,7 @@
         <v>44543</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7614,7 +7614,7 @@
         <v>44516</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7687,7 +7687,7 @@
         <v>44844</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7760,7 +7760,7 @@
         <v>44567</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7833,7 +7833,7 @@
         <v>44523</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7906,7 +7906,7 @@
         <v>44748</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7979,7 +7979,7 @@
         <v>44748</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8052,7 +8052,7 @@
         <v>44585</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8125,7 +8125,7 @@
         <v>44614</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8203,7 +8203,7 @@
         <v>44698</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8276,7 +8276,7 @@
         <v>44740</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8349,7 +8349,7 @@
         <v>44530</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8422,7 +8422,7 @@
         <v>44698</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8495,7 +8495,7 @@
         <v>44847</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8568,7 +8568,7 @@
         <v>44635</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8641,7 +8641,7 @@
         <v>44481</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8714,7 +8714,7 @@
         <v>44823</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8787,7 +8787,7 @@
         <v>44629</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8860,7 +8860,7 @@
         <v>44762</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8933,7 +8933,7 @@
         <v>44809</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9006,7 +9006,7 @@
         <v>44743</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9079,7 +9079,7 @@
         <v>44959</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9152,7 +9152,7 @@
         <v>45201</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9225,7 +9225,7 @@
         <v>45197</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9298,7 +9298,7 @@
         <v>45322</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9371,7 +9371,7 @@
         <v>45756</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9444,7 +9444,7 @@
         <v>46002</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9517,7 +9517,7 @@
         <v>46002</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9590,7 +9590,7 @@
         <v>45539</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9663,7 +9663,7 @@
         <v>46008</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9736,7 +9736,7 @@
         <v>46008</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9809,7 +9809,7 @@
         <v>45715</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9882,7 +9882,7 @@
         <v>45884</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9960,7 +9960,7 @@
         <v>45749</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10038,7 +10038,7 @@
         <v>45721</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10111,7 +10111,7 @@
         <v>44903</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10189,7 +10189,7 @@
         <v>46013</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10262,7 +10262,7 @@
         <v>45853</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10335,7 +10335,7 @@
         <v>44601</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10413,7 +10413,7 @@
         <v>45888</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10491,7 +10491,7 @@
         <v>45889</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10564,7 +10564,7 @@
         <v>45889</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10637,7 +10637,7 @@
         <v>45635</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10710,7 +10710,7 @@
         <v>46017</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10783,7 +10783,7 @@
         <v>45709</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10856,7 +10856,7 @@
         <v>45230</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10929,7 +10929,7 @@
         <v>45743</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11002,7 +11002,7 @@
         <v>45710</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11075,7 +11075,7 @@
         <v>45093</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11148,7 +11148,7 @@
         <v>45792</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11221,7 +11221,7 @@
         <v>45163</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11294,7 +11294,7 @@
         <v>46036</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11367,7 +11367,7 @@
         <v>45334</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11440,7 +11440,7 @@
         <v>45142</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11513,7 +11513,7 @@
         <v>45734</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11591,7 +11591,7 @@
         <v>45215</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11664,7 +11664,7 @@
         <v>45796</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11737,7 +11737,7 @@
         <v>45799</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11815,7 +11815,7 @@
         <v>45799</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11893,7 +11893,7 @@
         <v>45803</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11966,7 +11966,7 @@
         <v>46051</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12039,7 +12039,7 @@
         <v>45800</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12117,7 +12117,7 @@
         <v>45800</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12190,7 +12190,7 @@
         <v>46052</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12263,7 +12263,7 @@
         <v>45161</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12336,7 +12336,7 @@
         <v>45929</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12409,7 +12409,7 @@
         <v>45699</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12487,7 +12487,7 @@
         <v>45992</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12560,7 +12560,7 @@
         <v>46010</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12638,7 +12638,7 @@
         <v>45905</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12711,7 +12711,7 @@
         <v>46062</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12784,7 +12784,7 @@
         <v>46010</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12862,7 +12862,7 @@
         <v>45439</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12935,7 +12935,7 @@
         <v>46009</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13013,7 +13013,7 @@
         <v>46009</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13091,7 +13091,7 @@
         <v>46062</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13164,7 +13164,7 @@
         <v>45932</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13237,7 +13237,7 @@
         <v>44523</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13315,7 +13315,7 @@
         <v>45385</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13388,7 +13388,7 @@
         <v>45937</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13461,7 +13461,7 @@
         <v>45810</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13534,7 +13534,7 @@
         <v>45810</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13607,7 +13607,7 @@
         <v>45947</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13680,7 +13680,7 @@
         <v>45947</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13753,7 +13753,7 @@
         <v>45810</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13826,7 +13826,7 @@
         <v>45947</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13899,7 +13899,7 @@
         <v>45953</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13977,7 +13977,7 @@
         <v>45958</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14050,7 +14050,7 @@
         <v>46091</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14123,7 +14123,7 @@
         <v>44862</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14196,7 +14196,7 @@
         <v>46099</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14269,7 +14269,7 @@
         <v>45259</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14342,7 +14342,7 @@
         <v>45594</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14415,7 +14415,7 @@
         <v>45821</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14488,7 +14488,7 @@
         <v>45821</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14561,7 +14561,7 @@
         <v>45824</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14639,7 +14639,7 @@
         <v>45267</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14712,7 +14712,7 @@
         <v>45989</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14790,7 +14790,7 @@
         <v>45989</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14868,7 +14868,7 @@
         <v>45821</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14941,7 +14941,7 @@
         <v>45821</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15014,7 +15014,7 @@
         <v>45827</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15092,7 +15092,7 @@
         <v>45670</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15165,7 +15165,7 @@
         <v>46001</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15238,7 +15238,7 @@
         <v>46001</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15311,7 +15311,7 @@
         <v>46001</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15384,7 +15384,7 @@
         <v>45301</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15457,7 +15457,7 @@
         <v>45204</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15530,7 +15530,7 @@
         <v>45894</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15603,7 +15603,7 @@
         <v>45685</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15676,7 +15676,7 @@
         <v>45847</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15749,7 +15749,7 @@
         <v>45211</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15822,7 +15822,7 @@
         <v>44586</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15895,7 +15895,7 @@
         <v>45693</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15968,7 +15968,7 @@
         <v>45842</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16041,7 +16041,7 @@
         <v>45846</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16114,7 +16114,7 @@
         <v>45846</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16187,7 +16187,7 @@
         <v>45846</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16260,7 +16260,7 @@
         <v>45530</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16333,7 +16333,7 @@
         <v>45401</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16406,7 +16406,7 @@
         <v>44963</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16479,7 +16479,7 @@
         <v>45376</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16552,7 +16552,7 @@
         <v>44938</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16625,7 +16625,7 @@
         <v>45769</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16698,7 +16698,7 @@
         <v>45320</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16771,7 +16771,7 @@
         <v>44495</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16844,7 +16844,7 @@
         <v>44600</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16917,7 +16917,7 @@
         <v>44739</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16990,7 +16990,7 @@
         <v>45560</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17063,7 +17063,7 @@
         <v>45693</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17136,7 +17136,7 @@
         <v>45306</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17209,7 +17209,7 @@
         <v>46149</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17282,7 +17282,7 @@
         <v>45531</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17355,7 +17355,7 @@
         <v>45324</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17428,7 +17428,7 @@
         <v>45245</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17501,7 +17501,7 @@
         <v>45636</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17574,7 +17574,7 @@
         <v>45694</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17647,7 +17647,7 @@
         <v>46139</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17720,7 +17720,7 @@
         <v>45267</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17793,7 +17793,7 @@
         <v>46038</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17866,7 +17866,7 @@
         <v>45315</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17939,7 +17939,7 @@
         <v>45013</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18012,7 +18012,7 @@
         <v>46174</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -18085,7 +18085,7 @@
         <v>45586</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -18158,7 +18158,7 @@
         <v>45086</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -18231,7 +18231,7 @@
         <v>45006</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18304,7 +18304,7 @@
         <v>46182</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18377,7 +18377,7 @@
         <v>46182</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18450,7 +18450,7 @@
         <v>46185</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18523,7 +18523,7 @@
         <v>44796</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18596,7 +18596,7 @@
         <v>45076</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18669,7 +18669,7 @@
         <v>45742</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18742,7 +18742,7 @@
         <v>46202</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18815,7 +18815,7 @@
         <v>44599</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18893,7 +18893,7 @@
         <v>44750</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18971,7 +18971,7 @@
         <v>44636</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19044,7 +19044,7 @@
         <v>45105</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -19117,7 +19117,7 @@
         <v>45314</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -19190,7 +19190,7 @@
         <v>45259</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -19263,7 +19263,7 @@
         <v>46129</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19336,7 +19336,7 @@
         <v>44938</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19409,7 +19409,7 @@
         <v>46269</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19482,7 +19482,7 @@
         <v>46272</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19555,7 +19555,7 @@
         <v>44820</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19628,7 +19628,7 @@
         <v>45299</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19701,7 +19701,7 @@
         <v>45169</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19774,7 +19774,7 @@
         <v>45093</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19847,7 +19847,7 @@
         <v>45590</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19920,7 +19920,7 @@
         <v>45586</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19993,7 +19993,7 @@
         <v>46283</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20066,7 +20066,7 @@
         <v>45082</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -20139,7 +20139,7 @@
         <v>45687</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -20212,7 +20212,7 @@
         <v>45138</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20285,7 +20285,7 @@
         <v>46288</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20358,7 +20358,7 @@
         <v>45134</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20431,7 +20431,7 @@
         <v>46293</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20504,7 +20504,7 @@
         <v>45590</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20577,7 +20577,7 @@
         <v>45418</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20650,7 +20650,7 @@
         <v>45301</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20723,7 +20723,7 @@
         <v>46253</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20796,7 +20796,7 @@
         <v>44811</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20869,7 +20869,7 @@
         <v>45706</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20942,7 +20942,7 @@
         <v>45210</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -21015,7 +21015,7 @@
         <v>45002</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -21088,7 +21088,7 @@
         <v>45706</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -21161,7 +21161,7 @@
         <v>44825</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -21234,7 +21234,7 @@
         <v>45590</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -21307,7 +21307,7 @@
         <v>44804</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -21380,7 +21380,7 @@
         <v>45159</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21453,7 +21453,7 @@
         <v>45306</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21526,7 +21526,7 @@
         <v>45721</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21599,7 +21599,7 @@
         <v>45315</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21672,7 +21672,7 @@
         <v>45737</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21745,7 +21745,7 @@
         <v>45547</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21818,7 +21818,7 @@
         <v>45775</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21891,7 +21891,7 @@
         <v>44986</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21989,7 +21989,7 @@
         <v>45716</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>

--- a/Översikt SKÖVDE.xlsx
+++ b/Översikt SKÖVDE.xlsx
@@ -601,7 +601,7 @@
         <v>46196</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -736,7 +736,7 @@
         <v>46198</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -852,7 +852,7 @@
         <v>45876</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -966,7 +966,7 @@
         <v>45743</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1080,7 +1080,7 @@
         <v>44495</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1190,7 +1190,7 @@
         <v>46182</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1300,7 +1300,7 @@
         <v>45201</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1409,7 +1409,7 @@
         <v>46014</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1518,7 +1518,7 @@
         <v>46080</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1627,7 +1627,7 @@
         <v>44595</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1744,7 +1744,7 @@
         <v>44594</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1861,7 +1861,7 @@
         <v>45306</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1977,7 +1977,7 @@
         <v>44949</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2094,7 +2094,7 @@
         <v>45387</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2202,7 +2202,7 @@
         <v>45979</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2314,7 +2314,7 @@
         <v>45714</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2431,7 +2431,7 @@
         <v>44943</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2538,7 +2538,7 @@
         <v>44837</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2645,7 +2645,7 @@
         <v>44804</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2757,7 +2757,7 @@
         <v>45506</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2864,7 +2864,7 @@
         <v>45824</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2976,7 +2976,7 @@
         <v>44817</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3083,7 +3083,7 @@
         <v>44928</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3195,7 +3195,7 @@
         <v>45334</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3306,7 +3306,7 @@
         <v>45334</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3417,7 +3417,7 @@
         <v>46289</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3524,7 +3524,7 @@
         <v>45635</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3630,7 +3630,7 @@
         <v>44988</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3741,7 +3741,7 @@
         <v>45785</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3851,7 +3851,7 @@
         <v>45743</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3957,7 +3957,7 @@
         <v>45800</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4068,7 +4068,7 @@
         <v>45471</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4174,7 +4174,7 @@
         <v>45972</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4280,7 +4280,7 @@
         <v>44495</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4386,7 +4386,7 @@
         <v>45799</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4497,7 +4497,7 @@
         <v>44750</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4608,7 +4608,7 @@
         <v>45797</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4723,7 +4723,7 @@
         <v>46185</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4829,7 +4829,7 @@
         <v>45903</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4940,7 +4940,7 @@
         <v>44834</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5050,7 +5050,7 @@
         <v>45148</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5155,7 +5155,7 @@
         <v>45104</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5265,7 +5265,7 @@
         <v>45182</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5375,7 +5375,7 @@
         <v>44988</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5480,7 +5480,7 @@
         <v>45322</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5585,7 +5585,7 @@
         <v>45932</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5690,7 +5690,7 @@
         <v>45204</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5795,7 +5795,7 @@
         <v>45810</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5905,7 +5905,7 @@
         <v>45224</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6010,7 +6010,7 @@
         <v>45645</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6115,7 +6115,7 @@
         <v>45755</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6225,7 +6225,7 @@
         <v>45036</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6330,7 +6330,7 @@
         <v>45322</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6435,7 +6435,7 @@
         <v>45040</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6540,7 +6540,7 @@
         <v>46045</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6645,7 +6645,7 @@
         <v>46052</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6750,7 +6750,7 @@
         <v>46198</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6855,7 +6855,7 @@
         <v>46173</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6960,7 +6960,7 @@
         <v>46272</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7065,7 +7065,7 @@
         <v>45019</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7170,7 +7170,7 @@
         <v>44986</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7280,7 +7280,7 @@
         <v>44594</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7358,7 +7358,7 @@
         <v>44609</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7431,7 +7431,7 @@
         <v>44543</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7509,7 +7509,7 @@
         <v>44516</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7582,7 +7582,7 @@
         <v>44844</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7655,7 +7655,7 @@
         <v>44567</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7728,7 +7728,7 @@
         <v>44523</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7801,7 +7801,7 @@
         <v>44740</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7874,7 +7874,7 @@
         <v>44847</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7947,7 +7947,7 @@
         <v>44530</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8020,7 +8020,7 @@
         <v>44635</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8093,7 +8093,7 @@
         <v>44748</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8166,7 +8166,7 @@
         <v>44748</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8239,7 +8239,7 @@
         <v>44698</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8312,7 +8312,7 @@
         <v>44698</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8385,7 +8385,7 @@
         <v>44823</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8458,7 +8458,7 @@
         <v>44629</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8531,7 +8531,7 @@
         <v>44481</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8604,7 +8604,7 @@
         <v>44585</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8677,7 +8677,7 @@
         <v>44614</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8755,7 +8755,7 @@
         <v>44762</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8828,7 +8828,7 @@
         <v>44809</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8901,7 +8901,7 @@
         <v>45138</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8974,7 +8974,7 @@
         <v>44495</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9047,7 +9047,7 @@
         <v>45259</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9120,7 +9120,7 @@
         <v>45267</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9193,7 +9193,7 @@
         <v>44804</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9266,7 +9266,7 @@
         <v>45299</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9339,7 +9339,7 @@
         <v>45322</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9412,7 +9412,7 @@
         <v>45301</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9485,7 +9485,7 @@
         <v>45245</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9558,7 +9558,7 @@
         <v>45315</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9631,7 +9631,7 @@
         <v>45530</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9704,7 +9704,7 @@
         <v>45210</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9777,7 +9777,7 @@
         <v>44903</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9855,7 +9855,7 @@
         <v>44862</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9928,7 +9928,7 @@
         <v>45320</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10001,7 +10001,7 @@
         <v>45093</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10074,7 +10074,7 @@
         <v>45197</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10147,7 +10147,7 @@
         <v>45314</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10220,7 +10220,7 @@
         <v>45306</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10293,7 +10293,7 @@
         <v>45687</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10366,7 +10366,7 @@
         <v>45215</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10439,7 +10439,7 @@
         <v>45884</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10517,7 +10517,7 @@
         <v>44743</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10590,7 +10590,7 @@
         <v>45706</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10663,7 +10663,7 @@
         <v>45888</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10741,7 +10741,7 @@
         <v>45159</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10814,7 +10814,7 @@
         <v>45853</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10887,7 +10887,7 @@
         <v>45756</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10960,7 +10960,7 @@
         <v>45635</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11033,7 +11033,7 @@
         <v>45082</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11106,7 +11106,7 @@
         <v>45889</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11179,7 +11179,7 @@
         <v>45889</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11252,7 +11252,7 @@
         <v>44938</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11325,7 +11325,7 @@
         <v>45531</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11398,7 +11398,7 @@
         <v>45709</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11471,7 +11471,7 @@
         <v>45315</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11544,7 +11544,7 @@
         <v>45742</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11617,7 +11617,7 @@
         <v>45093</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11690,7 +11690,7 @@
         <v>44959</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11763,7 +11763,7 @@
         <v>45418</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11836,7 +11836,7 @@
         <v>45259</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11909,7 +11909,7 @@
         <v>45721</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11982,7 +11982,7 @@
         <v>45693</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12055,7 +12055,7 @@
         <v>45306</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12128,7 +12128,7 @@
         <v>45775</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12201,7 +12201,7 @@
         <v>45586</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12274,7 +12274,7 @@
         <v>45586</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12347,7 +12347,7 @@
         <v>45670</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12420,7 +12420,7 @@
         <v>45547</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12493,7 +12493,7 @@
         <v>44938</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12566,7 +12566,7 @@
         <v>45401</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12639,7 +12639,7 @@
         <v>45539</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12712,7 +12712,7 @@
         <v>44599</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12790,7 +12790,7 @@
         <v>45792</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12863,7 +12863,7 @@
         <v>45710</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12936,7 +12936,7 @@
         <v>45743</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13009,7 +13009,7 @@
         <v>45715</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13082,7 +13082,7 @@
         <v>45142</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13155,7 +13155,7 @@
         <v>45929</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13228,7 +13228,7 @@
         <v>45734</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13306,7 +13306,7 @@
         <v>45905</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13379,7 +13379,7 @@
         <v>45169</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13452,7 +13452,7 @@
         <v>45560</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13525,7 +13525,7 @@
         <v>45932</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13598,7 +13598,7 @@
         <v>45796</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13671,7 +13671,7 @@
         <v>45439</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13744,7 +13744,7 @@
         <v>45334</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13817,7 +13817,7 @@
         <v>45799</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13895,7 +13895,7 @@
         <v>45800</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13973,7 +13973,7 @@
         <v>45800</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14046,7 +14046,7 @@
         <v>45799</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14124,7 +14124,7 @@
         <v>45803</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14197,7 +14197,7 @@
         <v>45937</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14270,7 +14270,7 @@
         <v>45590</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14343,7 +14343,7 @@
         <v>44750</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14421,7 +14421,7 @@
         <v>45810</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14494,7 +14494,7 @@
         <v>45230</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14567,7 +14567,7 @@
         <v>45590</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14640,7 +14640,7 @@
         <v>45810</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14713,7 +14713,7 @@
         <v>45810</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14786,7 +14786,7 @@
         <v>45947</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14859,7 +14859,7 @@
         <v>45947</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14932,7 +14932,7 @@
         <v>45163</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15005,7 +15005,7 @@
         <v>45594</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15078,7 +15078,7 @@
         <v>45824</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15156,7 +15156,7 @@
         <v>45821</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15229,7 +15229,7 @@
         <v>45821</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15302,7 +15302,7 @@
         <v>45821</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15375,7 +15375,7 @@
         <v>45821</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15448,7 +15448,7 @@
         <v>45947</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15521,7 +15521,7 @@
         <v>45827</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15599,7 +15599,7 @@
         <v>44825</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15672,7 +15672,7 @@
         <v>45076</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15745,7 +15745,7 @@
         <v>45699</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15823,7 +15823,7 @@
         <v>45953</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15901,7 +15901,7 @@
         <v>45958</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15974,7 +15974,7 @@
         <v>45006</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16047,7 +16047,7 @@
         <v>45385</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16120,7 +16120,7 @@
         <v>45161</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16193,7 +16193,7 @@
         <v>45002</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16266,7 +16266,7 @@
         <v>45204</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16339,7 +16339,7 @@
         <v>45842</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16412,7 +16412,7 @@
         <v>45749</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16490,7 +16490,7 @@
         <v>45846</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16563,7 +16563,7 @@
         <v>45846</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16636,7 +16636,7 @@
         <v>45590</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16709,7 +16709,7 @@
         <v>45846</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16782,7 +16782,7 @@
         <v>44811</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16855,7 +16855,7 @@
         <v>45769</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16928,7 +16928,7 @@
         <v>45134</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17001,7 +17001,7 @@
         <v>45694</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17074,7 +17074,7 @@
         <v>44820</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17147,7 +17147,7 @@
         <v>45211</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17220,7 +17220,7 @@
         <v>45201</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17293,7 +17293,7 @@
         <v>44586</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17366,7 +17366,7 @@
         <v>45301</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17439,7 +17439,7 @@
         <v>44796</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17512,7 +17512,7 @@
         <v>44636</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17585,7 +17585,7 @@
         <v>46099</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17658,7 +17658,7 @@
         <v>45989</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17736,7 +17736,7 @@
         <v>44739</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17809,7 +17809,7 @@
         <v>45737</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17882,7 +17882,7 @@
         <v>45989</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17960,7 +17960,7 @@
         <v>45636</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -18033,7 +18033,7 @@
         <v>45706</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -18106,7 +18106,7 @@
         <v>45721</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -18179,7 +18179,7 @@
         <v>44601</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18257,7 +18257,7 @@
         <v>44963</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18330,7 +18330,7 @@
         <v>46001</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18403,7 +18403,7 @@
         <v>46002</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18476,7 +18476,7 @@
         <v>44600</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18549,7 +18549,7 @@
         <v>46002</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18622,7 +18622,7 @@
         <v>46001</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18695,7 +18695,7 @@
         <v>46001</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18768,7 +18768,7 @@
         <v>45894</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18841,7 +18841,7 @@
         <v>45847</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18914,7 +18914,7 @@
         <v>46008</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18987,7 +18987,7 @@
         <v>46008</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -19060,7 +19060,7 @@
         <v>46013</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -19133,7 +19133,7 @@
         <v>45693</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -19206,7 +19206,7 @@
         <v>46017</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19279,7 +19279,7 @@
         <v>45013</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19352,7 +19352,7 @@
         <v>44523</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19430,7 +19430,7 @@
         <v>46036</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19503,7 +19503,7 @@
         <v>45105</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19576,7 +19576,7 @@
         <v>45376</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19649,7 +19649,7 @@
         <v>45324</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19722,7 +19722,7 @@
         <v>45685</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19795,7 +19795,7 @@
         <v>45086</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19868,7 +19868,7 @@
         <v>46052</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19941,7 +19941,7 @@
         <v>46051</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20014,7 +20014,7 @@
         <v>46009</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -20092,7 +20092,7 @@
         <v>46010</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -20170,7 +20170,7 @@
         <v>46009</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20248,7 +20248,7 @@
         <v>46010</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20326,7 +20326,7 @@
         <v>46062</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20399,7 +20399,7 @@
         <v>45992</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20472,7 +20472,7 @@
         <v>46062</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20545,7 +20545,7 @@
         <v>46149</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20618,7 +20618,7 @@
         <v>46091</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20691,7 +20691,7 @@
         <v>46139</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20764,7 +20764,7 @@
         <v>45267</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20837,7 +20837,7 @@
         <v>46038</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20910,7 +20910,7 @@
         <v>46174</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20983,7 +20983,7 @@
         <v>46182</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -21056,7 +21056,7 @@
         <v>46182</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -21129,7 +21129,7 @@
         <v>46185</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -21202,7 +21202,7 @@
         <v>46202</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -21275,7 +21275,7 @@
         <v>46129</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -21348,7 +21348,7 @@
         <v>46272</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21421,7 +21421,7 @@
         <v>46269</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21494,7 +21494,7 @@
         <v>46283</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21567,7 +21567,7 @@
         <v>46288</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21640,7 +21640,7 @@
         <v>46293</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21713,7 +21713,7 @@
         <v>46253</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21786,7 +21786,7 @@
         <v>44986</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21884,7 +21884,7 @@
         <v>45716</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>

--- a/Översikt SKÖVDE.xlsx
+++ b/Översikt SKÖVDE.xlsx
@@ -601,7 +601,7 @@
         <v>46196</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -736,7 +736,7 @@
         <v>46198</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -852,7 +852,7 @@
         <v>45876</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -966,7 +966,7 @@
         <v>45743</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1080,7 +1080,7 @@
         <v>44495</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1190,7 +1190,7 @@
         <v>46182</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1300,7 +1300,7 @@
         <v>45201</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1409,7 +1409,7 @@
         <v>46014</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1518,7 +1518,7 @@
         <v>46080</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1627,7 +1627,7 @@
         <v>44595</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1744,7 +1744,7 @@
         <v>44594</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1861,7 +1861,7 @@
         <v>45306</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1977,7 +1977,7 @@
         <v>44949</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2094,7 +2094,7 @@
         <v>45387</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2202,7 +2202,7 @@
         <v>45979</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2314,7 +2314,7 @@
         <v>45714</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2431,7 +2431,7 @@
         <v>44943</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2538,7 +2538,7 @@
         <v>44837</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2645,7 +2645,7 @@
         <v>44804</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2757,7 +2757,7 @@
         <v>45506</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2864,7 +2864,7 @@
         <v>45824</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2976,7 +2976,7 @@
         <v>44817</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3083,7 +3083,7 @@
         <v>44928</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3195,7 +3195,7 @@
         <v>45334</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3306,7 +3306,7 @@
         <v>45334</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3417,7 +3417,7 @@
         <v>46289</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3524,7 +3524,7 @@
         <v>45635</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3630,7 +3630,7 @@
         <v>44988</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3741,7 +3741,7 @@
         <v>45785</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3851,7 +3851,7 @@
         <v>45743</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3957,7 +3957,7 @@
         <v>45800</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4068,7 +4068,7 @@
         <v>45471</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4174,7 +4174,7 @@
         <v>45972</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4280,7 +4280,7 @@
         <v>44495</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4386,7 +4386,7 @@
         <v>45799</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4497,7 +4497,7 @@
         <v>44750</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4608,7 +4608,7 @@
         <v>45797</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4723,7 +4723,7 @@
         <v>46185</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4829,7 +4829,7 @@
         <v>45903</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4940,7 +4940,7 @@
         <v>44834</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5050,7 +5050,7 @@
         <v>45148</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5155,7 +5155,7 @@
         <v>45104</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5265,7 +5265,7 @@
         <v>45182</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5375,7 +5375,7 @@
         <v>44988</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5480,7 +5480,7 @@
         <v>45322</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5585,7 +5585,7 @@
         <v>45932</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5690,7 +5690,7 @@
         <v>45204</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5795,7 +5795,7 @@
         <v>45810</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5905,7 +5905,7 @@
         <v>45224</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6010,7 +6010,7 @@
         <v>45645</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6115,7 +6115,7 @@
         <v>45755</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6225,7 +6225,7 @@
         <v>45036</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6330,7 +6330,7 @@
         <v>45322</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6435,7 +6435,7 @@
         <v>45040</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6540,7 +6540,7 @@
         <v>46045</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6645,7 +6645,7 @@
         <v>46052</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6750,7 +6750,7 @@
         <v>46198</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6855,7 +6855,7 @@
         <v>46173</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6960,7 +6960,7 @@
         <v>46272</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7065,7 +7065,7 @@
         <v>45019</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7170,7 +7170,7 @@
         <v>44986</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7280,7 +7280,7 @@
         <v>44594</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7358,7 +7358,7 @@
         <v>44609</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7431,7 +7431,7 @@
         <v>44543</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7509,7 +7509,7 @@
         <v>44516</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7582,7 +7582,7 @@
         <v>44844</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7655,7 +7655,7 @@
         <v>44567</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7728,7 +7728,7 @@
         <v>44523</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7801,7 +7801,7 @@
         <v>44740</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7874,7 +7874,7 @@
         <v>44847</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7947,7 +7947,7 @@
         <v>44530</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8020,7 +8020,7 @@
         <v>44635</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8093,7 +8093,7 @@
         <v>44748</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8166,7 +8166,7 @@
         <v>44748</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8239,7 +8239,7 @@
         <v>44698</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8312,7 +8312,7 @@
         <v>44698</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8385,7 +8385,7 @@
         <v>44823</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8458,7 +8458,7 @@
         <v>44629</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8531,7 +8531,7 @@
         <v>44481</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8604,7 +8604,7 @@
         <v>44585</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8677,7 +8677,7 @@
         <v>44614</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8755,7 +8755,7 @@
         <v>44762</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8828,7 +8828,7 @@
         <v>44809</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8901,7 +8901,7 @@
         <v>45138</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8974,7 +8974,7 @@
         <v>44495</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9047,7 +9047,7 @@
         <v>45259</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9120,7 +9120,7 @@
         <v>45267</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9193,7 +9193,7 @@
         <v>44804</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9266,7 +9266,7 @@
         <v>45299</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9339,7 +9339,7 @@
         <v>45322</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9412,7 +9412,7 @@
         <v>45301</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9485,7 +9485,7 @@
         <v>45245</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9558,7 +9558,7 @@
         <v>45315</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9631,7 +9631,7 @@
         <v>45530</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9704,7 +9704,7 @@
         <v>45210</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9777,7 +9777,7 @@
         <v>44903</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9855,7 +9855,7 @@
         <v>44862</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9928,7 +9928,7 @@
         <v>45320</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10001,7 +10001,7 @@
         <v>45093</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10074,7 +10074,7 @@
         <v>45197</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10147,7 +10147,7 @@
         <v>45314</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10220,7 +10220,7 @@
         <v>45306</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10293,7 +10293,7 @@
         <v>45687</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10366,7 +10366,7 @@
         <v>45215</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10439,7 +10439,7 @@
         <v>45884</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10517,7 +10517,7 @@
         <v>44743</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10590,7 +10590,7 @@
         <v>45706</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10663,7 +10663,7 @@
         <v>45888</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10741,7 +10741,7 @@
         <v>45159</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10814,7 +10814,7 @@
         <v>45853</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10887,7 +10887,7 @@
         <v>45756</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10960,7 +10960,7 @@
         <v>45635</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11033,7 +11033,7 @@
         <v>45082</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11106,7 +11106,7 @@
         <v>45889</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11179,7 +11179,7 @@
         <v>45889</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11252,7 +11252,7 @@
         <v>44938</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11325,7 +11325,7 @@
         <v>45531</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11398,7 +11398,7 @@
         <v>45709</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11471,7 +11471,7 @@
         <v>45315</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11544,7 +11544,7 @@
         <v>45742</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11617,7 +11617,7 @@
         <v>45093</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11690,7 +11690,7 @@
         <v>44959</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11763,7 +11763,7 @@
         <v>45418</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11836,7 +11836,7 @@
         <v>45259</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11909,7 +11909,7 @@
         <v>45721</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11982,7 +11982,7 @@
         <v>45693</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12055,7 +12055,7 @@
         <v>45306</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12128,7 +12128,7 @@
         <v>45775</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12201,7 +12201,7 @@
         <v>45586</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12274,7 +12274,7 @@
         <v>45586</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12347,7 +12347,7 @@
         <v>45670</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12420,7 +12420,7 @@
         <v>45547</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12493,7 +12493,7 @@
         <v>44938</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12566,7 +12566,7 @@
         <v>45401</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12639,7 +12639,7 @@
         <v>45539</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12712,7 +12712,7 @@
         <v>44599</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12790,7 +12790,7 @@
         <v>45792</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12863,7 +12863,7 @@
         <v>45710</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12936,7 +12936,7 @@
         <v>45743</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13009,7 +13009,7 @@
         <v>45715</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13082,7 +13082,7 @@
         <v>45142</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13155,7 +13155,7 @@
         <v>45929</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13228,7 +13228,7 @@
         <v>45734</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13306,7 +13306,7 @@
         <v>45905</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13379,7 +13379,7 @@
         <v>45169</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13452,7 +13452,7 @@
         <v>45560</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13525,7 +13525,7 @@
         <v>45932</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13598,7 +13598,7 @@
         <v>45796</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13671,7 +13671,7 @@
         <v>45439</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13744,7 +13744,7 @@
         <v>45334</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13817,7 +13817,7 @@
         <v>45799</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13895,7 +13895,7 @@
         <v>45800</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13973,7 +13973,7 @@
         <v>45800</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14046,7 +14046,7 @@
         <v>45799</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14124,7 +14124,7 @@
         <v>45803</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14197,7 +14197,7 @@
         <v>45937</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14270,7 +14270,7 @@
         <v>45590</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14343,7 +14343,7 @@
         <v>44750</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14421,7 +14421,7 @@
         <v>45810</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14494,7 +14494,7 @@
         <v>45230</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14567,7 +14567,7 @@
         <v>45590</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14640,7 +14640,7 @@
         <v>45810</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14713,7 +14713,7 @@
         <v>45810</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14786,7 +14786,7 @@
         <v>45947</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14859,7 +14859,7 @@
         <v>45947</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14932,7 +14932,7 @@
         <v>45163</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15005,7 +15005,7 @@
         <v>45594</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15078,7 +15078,7 @@
         <v>45824</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15156,7 +15156,7 @@
         <v>45821</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15229,7 +15229,7 @@
         <v>45821</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15302,7 +15302,7 @@
         <v>45821</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15375,7 +15375,7 @@
         <v>45821</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15448,7 +15448,7 @@
         <v>45947</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15521,7 +15521,7 @@
         <v>45827</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15599,7 +15599,7 @@
         <v>44825</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15672,7 +15672,7 @@
         <v>45076</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15745,7 +15745,7 @@
         <v>45699</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15823,7 +15823,7 @@
         <v>45953</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15901,7 +15901,7 @@
         <v>45958</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15974,7 +15974,7 @@
         <v>45006</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16047,7 +16047,7 @@
         <v>45385</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16120,7 +16120,7 @@
         <v>45161</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16193,7 +16193,7 @@
         <v>45002</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16266,7 +16266,7 @@
         <v>45204</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16339,7 +16339,7 @@
         <v>45842</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16412,7 +16412,7 @@
         <v>45749</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16490,7 +16490,7 @@
         <v>45846</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16563,7 +16563,7 @@
         <v>45846</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16636,7 +16636,7 @@
         <v>45590</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16709,7 +16709,7 @@
         <v>45846</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16782,7 +16782,7 @@
         <v>44811</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16855,7 +16855,7 @@
         <v>45769</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16928,7 +16928,7 @@
         <v>45134</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17001,7 +17001,7 @@
         <v>45694</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17074,7 +17074,7 @@
         <v>44820</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17147,7 +17147,7 @@
         <v>45211</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17220,7 +17220,7 @@
         <v>45201</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17293,7 +17293,7 @@
         <v>44586</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17366,7 +17366,7 @@
         <v>45301</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17439,7 +17439,7 @@
         <v>44796</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17512,7 +17512,7 @@
         <v>44636</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17585,7 +17585,7 @@
         <v>46099</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17658,7 +17658,7 @@
         <v>45989</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17736,7 +17736,7 @@
         <v>44739</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17809,7 +17809,7 @@
         <v>45737</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17882,7 +17882,7 @@
         <v>45989</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17960,7 +17960,7 @@
         <v>45636</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -18033,7 +18033,7 @@
         <v>45706</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -18106,7 +18106,7 @@
         <v>45721</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -18179,7 +18179,7 @@
         <v>44601</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18257,7 +18257,7 @@
         <v>44963</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18330,7 +18330,7 @@
         <v>46001</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18403,7 +18403,7 @@
         <v>46002</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18476,7 +18476,7 @@
         <v>44600</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18549,7 +18549,7 @@
         <v>46002</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18622,7 +18622,7 @@
         <v>46001</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18695,7 +18695,7 @@
         <v>46001</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18768,7 +18768,7 @@
         <v>45894</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18841,7 +18841,7 @@
         <v>45847</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18914,7 +18914,7 @@
         <v>46008</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18987,7 +18987,7 @@
         <v>46008</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -19060,7 +19060,7 @@
         <v>46013</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -19133,7 +19133,7 @@
         <v>45693</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -19206,7 +19206,7 @@
         <v>46017</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19279,7 +19279,7 @@
         <v>45013</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19352,7 +19352,7 @@
         <v>44523</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19430,7 +19430,7 @@
         <v>46036</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19503,7 +19503,7 @@
         <v>45105</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19576,7 +19576,7 @@
         <v>45376</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19649,7 +19649,7 @@
         <v>45324</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19722,7 +19722,7 @@
         <v>45685</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19795,7 +19795,7 @@
         <v>45086</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19868,7 +19868,7 @@
         <v>46052</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19941,7 +19941,7 @@
         <v>46051</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20014,7 +20014,7 @@
         <v>46009</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -20092,7 +20092,7 @@
         <v>46010</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -20170,7 +20170,7 @@
         <v>46009</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20248,7 +20248,7 @@
         <v>46010</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20326,7 +20326,7 @@
         <v>46062</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20399,7 +20399,7 @@
         <v>45992</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20472,7 +20472,7 @@
         <v>46062</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20545,7 +20545,7 @@
         <v>46149</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20618,7 +20618,7 @@
         <v>46091</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20691,7 +20691,7 @@
         <v>46139</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20764,7 +20764,7 @@
         <v>45267</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20837,7 +20837,7 @@
         <v>46038</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20910,7 +20910,7 @@
         <v>46174</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20983,7 +20983,7 @@
         <v>46182</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -21056,7 +21056,7 @@
         <v>46182</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -21129,7 +21129,7 @@
         <v>46185</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -21202,7 +21202,7 @@
         <v>46202</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -21275,7 +21275,7 @@
         <v>46129</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -21348,7 +21348,7 @@
         <v>46272</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21421,7 +21421,7 @@
         <v>46269</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21494,7 +21494,7 @@
         <v>46283</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21567,7 +21567,7 @@
         <v>46288</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21640,7 +21640,7 @@
         <v>46293</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21713,7 +21713,7 @@
         <v>46253</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21786,7 +21786,7 @@
         <v>44986</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21884,7 +21884,7 @@
         <v>45716</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>

--- a/Översikt SKÖVDE.xlsx
+++ b/Översikt SKÖVDE.xlsx
@@ -601,7 +601,7 @@
         <v>46196</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -736,7 +736,7 @@
         <v>46198</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -852,7 +852,7 @@
         <v>45876</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -966,7 +966,7 @@
         <v>45743</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1080,7 +1080,7 @@
         <v>46182</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1190,7 +1190,7 @@
         <v>44495</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1300,7 +1300,7 @@
         <v>46014</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1409,7 +1409,7 @@
         <v>45201</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1518,7 +1518,7 @@
         <v>46080</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1627,7 +1627,7 @@
         <v>44595</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1744,7 +1744,7 @@
         <v>44594</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1861,7 +1861,7 @@
         <v>45306</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1977,7 +1977,7 @@
         <v>45979</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2089,7 +2089,7 @@
         <v>45714</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2206,7 +2206,7 @@
         <v>44949</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2323,7 +2323,7 @@
         <v>45387</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2431,7 +2431,7 @@
         <v>45334</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2542,7 +2542,7 @@
         <v>45334</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2653,7 +2653,7 @@
         <v>44928</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2765,7 +2765,7 @@
         <v>44943</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2872,7 +2872,7 @@
         <v>44804</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2984,7 +2984,7 @@
         <v>44817</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3091,7 +3091,7 @@
         <v>46289</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3198,7 +3198,7 @@
         <v>44837</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3305,7 +3305,7 @@
         <v>45506</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3412,7 +3412,7 @@
         <v>45824</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3524,7 +3524,7 @@
         <v>45799</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3635,7 +3635,7 @@
         <v>45635</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3741,7 +3741,7 @@
         <v>45972</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3847,7 +3847,7 @@
         <v>45797</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3962,7 +3962,7 @@
         <v>46185</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4068,7 +4068,7 @@
         <v>44988</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4179,7 +4179,7 @@
         <v>44495</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4285,7 +4285,7 @@
         <v>44750</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4396,7 +4396,7 @@
         <v>45903</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4507,7 +4507,7 @@
         <v>45785</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4617,7 +4617,7 @@
         <v>45743</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4723,7 +4723,7 @@
         <v>45471</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4829,7 +4829,7 @@
         <v>45800</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4940,7 +4940,7 @@
         <v>44834</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5050,7 +5050,7 @@
         <v>44988</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5155,7 +5155,7 @@
         <v>45148</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5260,7 +5260,7 @@
         <v>45755</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5370,7 +5370,7 @@
         <v>45322</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5475,7 +5475,7 @@
         <v>45932</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5580,7 +5580,7 @@
         <v>46198</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5685,7 +5685,7 @@
         <v>45204</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5790,7 +5790,7 @@
         <v>45645</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5895,7 +5895,7 @@
         <v>45182</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6005,7 +6005,7 @@
         <v>45224</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6110,7 +6110,7 @@
         <v>46045</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6215,7 +6215,7 @@
         <v>46052</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6320,7 +6320,7 @@
         <v>46173</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6425,7 +6425,7 @@
         <v>45104</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6535,7 +6535,7 @@
         <v>46272</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6640,7 +6640,7 @@
         <v>45040</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6745,7 +6745,7 @@
         <v>45036</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6850,7 +6850,7 @@
         <v>45019</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6955,7 +6955,7 @@
         <v>45322</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7060,7 +7060,7 @@
         <v>45810</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7170,7 +7170,7 @@
         <v>44986</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7280,7 +7280,7 @@
         <v>44594</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7358,7 +7358,7 @@
         <v>44609</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7431,7 +7431,7 @@
         <v>44543</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7509,7 +7509,7 @@
         <v>44516</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7582,7 +7582,7 @@
         <v>44844</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7655,7 +7655,7 @@
         <v>44567</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7728,7 +7728,7 @@
         <v>44523</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7801,7 +7801,7 @@
         <v>44748</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7874,7 +7874,7 @@
         <v>44748</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7947,7 +7947,7 @@
         <v>44585</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8020,7 +8020,7 @@
         <v>44614</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8098,7 +8098,7 @@
         <v>44698</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8171,7 +8171,7 @@
         <v>44740</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8244,7 +8244,7 @@
         <v>44530</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8317,7 +8317,7 @@
         <v>44698</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8390,7 +8390,7 @@
         <v>44847</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8463,7 +8463,7 @@
         <v>44635</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8536,7 +8536,7 @@
         <v>44823</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8609,7 +8609,7 @@
         <v>44629</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8682,7 +8682,7 @@
         <v>44762</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8755,7 +8755,7 @@
         <v>44809</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8828,7 +8828,7 @@
         <v>44743</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8901,7 +8901,7 @@
         <v>44959</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8974,7 +8974,7 @@
         <v>45201</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9047,7 +9047,7 @@
         <v>45197</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9120,7 +9120,7 @@
         <v>45322</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9193,7 +9193,7 @@
         <v>45539</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9266,7 +9266,7 @@
         <v>45749</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9344,7 +9344,7 @@
         <v>45721</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9417,7 +9417,7 @@
         <v>44601</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9495,7 +9495,7 @@
         <v>44903</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9573,7 +9573,7 @@
         <v>45230</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9646,7 +9646,7 @@
         <v>45093</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9719,7 +9719,7 @@
         <v>45163</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9792,7 +9792,7 @@
         <v>45215</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9865,7 +9865,7 @@
         <v>45161</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9938,7 +9938,7 @@
         <v>45699</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10016,7 +10016,7 @@
         <v>45385</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10089,7 +10089,7 @@
         <v>44523</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10167,7 +10167,7 @@
         <v>44862</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10240,7 +10240,7 @@
         <v>45439</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10313,7 +10313,7 @@
         <v>45259</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10386,7 +10386,7 @@
         <v>45594</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10459,7 +10459,7 @@
         <v>45693</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10532,7 +10532,7 @@
         <v>45267</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10605,7 +10605,7 @@
         <v>45884</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10683,7 +10683,7 @@
         <v>45853</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10756,7 +10756,7 @@
         <v>45670</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10829,7 +10829,7 @@
         <v>45888</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10907,7 +10907,7 @@
         <v>45889</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10980,7 +10980,7 @@
         <v>45889</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11053,7 +11053,7 @@
         <v>45635</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11126,7 +11126,7 @@
         <v>45709</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11199,7 +11199,7 @@
         <v>45756</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11272,7 +11272,7 @@
         <v>45376</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11345,7 +11345,7 @@
         <v>45301</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11418,7 +11418,7 @@
         <v>45204</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11491,7 +11491,7 @@
         <v>45211</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11564,7 +11564,7 @@
         <v>44586</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11637,7 +11637,7 @@
         <v>46149</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11710,7 +11710,7 @@
         <v>45929</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11783,7 +11783,7 @@
         <v>45530</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11856,7 +11856,7 @@
         <v>45905</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11929,7 +11929,7 @@
         <v>45932</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12002,7 +12002,7 @@
         <v>45937</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12075,7 +12075,7 @@
         <v>45401</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12148,7 +12148,7 @@
         <v>44963</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12221,7 +12221,7 @@
         <v>44938</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12294,7 +12294,7 @@
         <v>45320</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12367,7 +12367,7 @@
         <v>45947</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12440,7 +12440,7 @@
         <v>44495</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12513,7 +12513,7 @@
         <v>45947</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12586,7 +12586,7 @@
         <v>45947</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12659,7 +12659,7 @@
         <v>45953</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12737,7 +12737,7 @@
         <v>44600</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12810,7 +12810,7 @@
         <v>45958</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12883,7 +12883,7 @@
         <v>44739</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12956,7 +12956,7 @@
         <v>45560</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13029,7 +13029,7 @@
         <v>46139</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13102,7 +13102,7 @@
         <v>45267</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13175,7 +13175,7 @@
         <v>45693</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13248,7 +13248,7 @@
         <v>45306</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13321,7 +13321,7 @@
         <v>45531</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13394,7 +13394,7 @@
         <v>46038</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13467,7 +13467,7 @@
         <v>45324</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13540,7 +13540,7 @@
         <v>45245</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13613,7 +13613,7 @@
         <v>45636</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13686,7 +13686,7 @@
         <v>45694</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13759,7 +13759,7 @@
         <v>45989</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13837,7 +13837,7 @@
         <v>45989</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13915,7 +13915,7 @@
         <v>46001</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13988,7 +13988,7 @@
         <v>46001</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14061,7 +14061,7 @@
         <v>46001</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14134,7 +14134,7 @@
         <v>45315</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14207,7 +14207,7 @@
         <v>46002</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14280,7 +14280,7 @@
         <v>46002</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14353,7 +14353,7 @@
         <v>46008</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14426,7 +14426,7 @@
         <v>46008</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14499,7 +14499,7 @@
         <v>45013</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14572,7 +14572,7 @@
         <v>46013</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14645,7 +14645,7 @@
         <v>45586</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14718,7 +14718,7 @@
         <v>45086</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14791,7 +14791,7 @@
         <v>46017</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14864,7 +14864,7 @@
         <v>46174</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14937,7 +14937,7 @@
         <v>45006</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15010,7 +15010,7 @@
         <v>46036</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15083,7 +15083,7 @@
         <v>44796</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15156,7 +15156,7 @@
         <v>46051</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15229,7 +15229,7 @@
         <v>45076</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15302,7 +15302,7 @@
         <v>46052</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15375,7 +15375,7 @@
         <v>46182</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15448,7 +15448,7 @@
         <v>46182</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15521,7 +15521,7 @@
         <v>45992</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15594,7 +15594,7 @@
         <v>46010</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15672,7 +15672,7 @@
         <v>46062</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15745,7 +15745,7 @@
         <v>46010</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15823,7 +15823,7 @@
         <v>46009</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15901,7 +15901,7 @@
         <v>46009</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15979,7 +15979,7 @@
         <v>46062</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16052,7 +16052,7 @@
         <v>45742</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16125,7 +16125,7 @@
         <v>46185</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16198,7 +16198,7 @@
         <v>44599</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16276,7 +16276,7 @@
         <v>44750</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16354,7 +16354,7 @@
         <v>44636</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16427,7 +16427,7 @@
         <v>45105</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16500,7 +16500,7 @@
         <v>45314</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16573,7 +16573,7 @@
         <v>46091</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16646,7 +16646,7 @@
         <v>45259</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16719,7 +16719,7 @@
         <v>46099</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16792,7 +16792,7 @@
         <v>44938</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16865,7 +16865,7 @@
         <v>46202</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16938,7 +16938,7 @@
         <v>44820</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17011,7 +17011,7 @@
         <v>45299</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17084,7 +17084,7 @@
         <v>45894</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17157,7 +17157,7 @@
         <v>45169</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17230,7 +17230,7 @@
         <v>45093</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17303,7 +17303,7 @@
         <v>45685</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17376,7 +17376,7 @@
         <v>45847</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17449,7 +17449,7 @@
         <v>45590</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17522,7 +17522,7 @@
         <v>45586</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17595,7 +17595,7 @@
         <v>45082</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17668,7 +17668,7 @@
         <v>45687</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17741,7 +17741,7 @@
         <v>45138</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17814,7 +17814,7 @@
         <v>46129</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17887,7 +17887,7 @@
         <v>45134</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17960,7 +17960,7 @@
         <v>46272</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -18033,7 +18033,7 @@
         <v>45590</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -18106,7 +18106,7 @@
         <v>45418</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -18179,7 +18179,7 @@
         <v>45301</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18252,7 +18252,7 @@
         <v>46283</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18325,7 +18325,7 @@
         <v>44811</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18398,7 +18398,7 @@
         <v>45706</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18471,7 +18471,7 @@
         <v>45210</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18544,7 +18544,7 @@
         <v>45002</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18617,7 +18617,7 @@
         <v>46288</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18690,7 +18690,7 @@
         <v>45706</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18763,7 +18763,7 @@
         <v>44825</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18836,7 +18836,7 @@
         <v>45590</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18909,7 +18909,7 @@
         <v>46293</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18982,7 +18982,7 @@
         <v>44804</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -19055,7 +19055,7 @@
         <v>45159</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -19128,7 +19128,7 @@
         <v>45306</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -19201,7 +19201,7 @@
         <v>45721</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19274,7 +19274,7 @@
         <v>46253</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19347,7 +19347,7 @@
         <v>45315</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19420,7 +19420,7 @@
         <v>45737</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19493,7 +19493,7 @@
         <v>45547</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19566,7 +19566,7 @@
         <v>45775</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19639,7 +19639,7 @@
         <v>45715</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19712,7 +19712,7 @@
         <v>45743</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19785,7 +19785,7 @@
         <v>45710</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19858,7 +19858,7 @@
         <v>45792</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19931,7 +19931,7 @@
         <v>45334</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20004,7 +20004,7 @@
         <v>45142</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -20077,7 +20077,7 @@
         <v>45734</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -20155,7 +20155,7 @@
         <v>45796</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20228,7 +20228,7 @@
         <v>45799</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20306,7 +20306,7 @@
         <v>45799</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20384,7 +20384,7 @@
         <v>45803</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20457,7 +20457,7 @@
         <v>45800</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20535,7 +20535,7 @@
         <v>45800</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20608,7 +20608,7 @@
         <v>45810</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20681,7 +20681,7 @@
         <v>45810</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20754,7 +20754,7 @@
         <v>45810</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20827,7 +20827,7 @@
         <v>46269</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20900,7 +20900,7 @@
         <v>45821</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20973,7 +20973,7 @@
         <v>45821</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -21046,7 +21046,7 @@
         <v>45824</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -21124,7 +21124,7 @@
         <v>45821</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -21197,7 +21197,7 @@
         <v>45821</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -21270,7 +21270,7 @@
         <v>45827</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -21348,7 +21348,7 @@
         <v>45842</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21421,7 +21421,7 @@
         <v>45846</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21494,7 +21494,7 @@
         <v>45846</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21567,7 +21567,7 @@
         <v>45846</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21640,7 +21640,7 @@
         <v>45769</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21713,7 +21713,7 @@
         <v>44986</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21811,7 +21811,7 @@
         <v>45716</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>

--- a/Översikt SKÖVDE.xlsx
+++ b/Översikt SKÖVDE.xlsx
@@ -601,7 +601,7 @@
         <v>46196</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -736,7 +736,7 @@
         <v>46198</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -852,7 +852,7 @@
         <v>45876</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -966,7 +966,7 @@
         <v>45743</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1080,7 +1080,7 @@
         <v>46182</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1190,7 +1190,7 @@
         <v>44495</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1300,7 +1300,7 @@
         <v>46014</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1409,7 +1409,7 @@
         <v>45201</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1518,7 +1518,7 @@
         <v>46080</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1627,7 +1627,7 @@
         <v>44595</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1744,7 +1744,7 @@
         <v>44594</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1861,7 +1861,7 @@
         <v>45306</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1977,7 +1977,7 @@
         <v>45979</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2089,7 +2089,7 @@
         <v>45714</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2206,7 +2206,7 @@
         <v>44949</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2323,7 +2323,7 @@
         <v>45387</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2431,7 +2431,7 @@
         <v>45334</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2542,7 +2542,7 @@
         <v>45334</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2653,7 +2653,7 @@
         <v>44928</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2765,7 +2765,7 @@
         <v>44943</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2872,7 +2872,7 @@
         <v>44804</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2984,7 +2984,7 @@
         <v>44817</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3091,7 +3091,7 @@
         <v>46289</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3198,7 +3198,7 @@
         <v>44837</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3305,7 +3305,7 @@
         <v>45506</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3412,7 +3412,7 @@
         <v>45824</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3524,7 +3524,7 @@
         <v>45799</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3635,7 +3635,7 @@
         <v>45635</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3741,7 +3741,7 @@
         <v>45972</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3847,7 +3847,7 @@
         <v>45797</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3962,7 +3962,7 @@
         <v>46185</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4068,7 +4068,7 @@
         <v>44988</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4179,7 +4179,7 @@
         <v>44495</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4285,7 +4285,7 @@
         <v>44750</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4396,7 +4396,7 @@
         <v>45903</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4507,7 +4507,7 @@
         <v>45785</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4617,7 +4617,7 @@
         <v>45743</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4723,7 +4723,7 @@
         <v>45471</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4829,7 +4829,7 @@
         <v>45800</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4940,7 +4940,7 @@
         <v>44834</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5050,7 +5050,7 @@
         <v>44988</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5155,7 +5155,7 @@
         <v>45148</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5260,7 +5260,7 @@
         <v>45755</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5370,7 +5370,7 @@
         <v>45322</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5475,7 +5475,7 @@
         <v>45932</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5580,7 +5580,7 @@
         <v>46198</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5685,7 +5685,7 @@
         <v>45204</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5790,7 +5790,7 @@
         <v>45645</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5895,7 +5895,7 @@
         <v>45182</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6005,7 +6005,7 @@
         <v>45224</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6110,7 +6110,7 @@
         <v>46045</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6215,7 +6215,7 @@
         <v>46052</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6320,7 +6320,7 @@
         <v>46173</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6425,7 +6425,7 @@
         <v>45104</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6535,7 +6535,7 @@
         <v>46272</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6640,7 +6640,7 @@
         <v>45040</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6745,7 +6745,7 @@
         <v>45036</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6850,7 +6850,7 @@
         <v>45019</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6955,7 +6955,7 @@
         <v>45322</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7060,7 +7060,7 @@
         <v>45810</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7170,7 +7170,7 @@
         <v>44986</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7280,7 +7280,7 @@
         <v>44594</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7358,7 +7358,7 @@
         <v>44609</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7431,7 +7431,7 @@
         <v>44543</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7509,7 +7509,7 @@
         <v>44516</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7582,7 +7582,7 @@
         <v>44844</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7655,7 +7655,7 @@
         <v>44567</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7728,7 +7728,7 @@
         <v>44523</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7801,7 +7801,7 @@
         <v>44748</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7874,7 +7874,7 @@
         <v>44748</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7947,7 +7947,7 @@
         <v>44585</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8020,7 +8020,7 @@
         <v>44614</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8098,7 +8098,7 @@
         <v>44698</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8171,7 +8171,7 @@
         <v>44740</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8244,7 +8244,7 @@
         <v>44530</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8317,7 +8317,7 @@
         <v>44698</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8390,7 +8390,7 @@
         <v>44847</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8463,7 +8463,7 @@
         <v>44635</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8536,7 +8536,7 @@
         <v>44823</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8609,7 +8609,7 @@
         <v>44629</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8682,7 +8682,7 @@
         <v>44762</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8755,7 +8755,7 @@
         <v>44809</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8828,7 +8828,7 @@
         <v>44743</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8901,7 +8901,7 @@
         <v>44959</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8974,7 +8974,7 @@
         <v>45201</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9047,7 +9047,7 @@
         <v>45197</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9120,7 +9120,7 @@
         <v>45322</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9193,7 +9193,7 @@
         <v>45539</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9266,7 +9266,7 @@
         <v>45749</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9344,7 +9344,7 @@
         <v>45721</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9417,7 +9417,7 @@
         <v>44601</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9495,7 +9495,7 @@
         <v>44903</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9573,7 +9573,7 @@
         <v>45230</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9646,7 +9646,7 @@
         <v>45093</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9719,7 +9719,7 @@
         <v>45163</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9792,7 +9792,7 @@
         <v>45215</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9865,7 +9865,7 @@
         <v>45161</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9938,7 +9938,7 @@
         <v>45699</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10016,7 +10016,7 @@
         <v>45385</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10089,7 +10089,7 @@
         <v>44523</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10167,7 +10167,7 @@
         <v>44862</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10240,7 +10240,7 @@
         <v>45439</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10313,7 +10313,7 @@
         <v>45259</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10386,7 +10386,7 @@
         <v>45594</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10459,7 +10459,7 @@
         <v>45693</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10532,7 +10532,7 @@
         <v>45267</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10605,7 +10605,7 @@
         <v>45884</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10683,7 +10683,7 @@
         <v>45853</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10756,7 +10756,7 @@
         <v>45670</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10829,7 +10829,7 @@
         <v>45888</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10907,7 +10907,7 @@
         <v>45889</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10980,7 +10980,7 @@
         <v>45889</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11053,7 +11053,7 @@
         <v>45635</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11126,7 +11126,7 @@
         <v>45709</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11199,7 +11199,7 @@
         <v>45756</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11272,7 +11272,7 @@
         <v>45376</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11345,7 +11345,7 @@
         <v>45301</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11418,7 +11418,7 @@
         <v>45204</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11491,7 +11491,7 @@
         <v>45211</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11564,7 +11564,7 @@
         <v>44586</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11637,7 +11637,7 @@
         <v>46149</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11710,7 +11710,7 @@
         <v>45929</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11783,7 +11783,7 @@
         <v>45530</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11856,7 +11856,7 @@
         <v>45905</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11929,7 +11929,7 @@
         <v>45932</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12002,7 +12002,7 @@
         <v>45937</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12075,7 +12075,7 @@
         <v>45401</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12148,7 +12148,7 @@
         <v>44963</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12221,7 +12221,7 @@
         <v>44938</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12294,7 +12294,7 @@
         <v>45320</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12367,7 +12367,7 @@
         <v>45947</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12440,7 +12440,7 @@
         <v>44495</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12513,7 +12513,7 @@
         <v>45947</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12586,7 +12586,7 @@
         <v>45947</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12659,7 +12659,7 @@
         <v>45953</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12737,7 +12737,7 @@
         <v>44600</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12810,7 +12810,7 @@
         <v>45958</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12883,7 +12883,7 @@
         <v>44739</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12956,7 +12956,7 @@
         <v>45560</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13029,7 +13029,7 @@
         <v>46139</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13102,7 +13102,7 @@
         <v>45267</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13175,7 +13175,7 @@
         <v>45693</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13248,7 +13248,7 @@
         <v>45306</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13321,7 +13321,7 @@
         <v>45531</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13394,7 +13394,7 @@
         <v>46038</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13467,7 +13467,7 @@
         <v>45324</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13540,7 +13540,7 @@
         <v>45245</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13613,7 +13613,7 @@
         <v>45636</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13686,7 +13686,7 @@
         <v>45694</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13759,7 +13759,7 @@
         <v>45989</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13837,7 +13837,7 @@
         <v>45989</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13915,7 +13915,7 @@
         <v>46001</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13988,7 +13988,7 @@
         <v>46001</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14061,7 +14061,7 @@
         <v>46001</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14134,7 +14134,7 @@
         <v>45315</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14207,7 +14207,7 @@
         <v>46002</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14280,7 +14280,7 @@
         <v>46002</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14353,7 +14353,7 @@
         <v>46008</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14426,7 +14426,7 @@
         <v>46008</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14499,7 +14499,7 @@
         <v>45013</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14572,7 +14572,7 @@
         <v>46013</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14645,7 +14645,7 @@
         <v>45586</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14718,7 +14718,7 @@
         <v>45086</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14791,7 +14791,7 @@
         <v>46017</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14864,7 +14864,7 @@
         <v>46174</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14937,7 +14937,7 @@
         <v>45006</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15010,7 +15010,7 @@
         <v>46036</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15083,7 +15083,7 @@
         <v>44796</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15156,7 +15156,7 @@
         <v>46051</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15229,7 +15229,7 @@
         <v>45076</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15302,7 +15302,7 @@
         <v>46052</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15375,7 +15375,7 @@
         <v>46182</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15448,7 +15448,7 @@
         <v>46182</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15521,7 +15521,7 @@
         <v>45992</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15594,7 +15594,7 @@
         <v>46010</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15672,7 +15672,7 @@
         <v>46062</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15745,7 +15745,7 @@
         <v>46010</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15823,7 +15823,7 @@
         <v>46009</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15901,7 +15901,7 @@
         <v>46009</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15979,7 +15979,7 @@
         <v>46062</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16052,7 +16052,7 @@
         <v>45742</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16125,7 +16125,7 @@
         <v>46185</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16198,7 +16198,7 @@
         <v>44599</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16276,7 +16276,7 @@
         <v>44750</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16354,7 +16354,7 @@
         <v>44636</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16427,7 +16427,7 @@
         <v>45105</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16500,7 +16500,7 @@
         <v>45314</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16573,7 +16573,7 @@
         <v>46091</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16646,7 +16646,7 @@
         <v>45259</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16719,7 +16719,7 @@
         <v>46099</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16792,7 +16792,7 @@
         <v>44938</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16865,7 +16865,7 @@
         <v>46202</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16938,7 +16938,7 @@
         <v>44820</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17011,7 +17011,7 @@
         <v>45299</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17084,7 +17084,7 @@
         <v>45894</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17157,7 +17157,7 @@
         <v>45169</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17230,7 +17230,7 @@
         <v>45093</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17303,7 +17303,7 @@
         <v>45685</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17376,7 +17376,7 @@
         <v>45847</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17449,7 +17449,7 @@
         <v>45590</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17522,7 +17522,7 @@
         <v>45586</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17595,7 +17595,7 @@
         <v>45082</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17668,7 +17668,7 @@
         <v>45687</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17741,7 +17741,7 @@
         <v>45138</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17814,7 +17814,7 @@
         <v>46129</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17887,7 +17887,7 @@
         <v>45134</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17960,7 +17960,7 @@
         <v>46272</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -18033,7 +18033,7 @@
         <v>45590</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -18106,7 +18106,7 @@
         <v>45418</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -18179,7 +18179,7 @@
         <v>45301</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18252,7 +18252,7 @@
         <v>46283</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18325,7 +18325,7 @@
         <v>44811</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18398,7 +18398,7 @@
         <v>45706</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18471,7 +18471,7 @@
         <v>45210</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18544,7 +18544,7 @@
         <v>45002</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18617,7 +18617,7 @@
         <v>46288</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18690,7 +18690,7 @@
         <v>45706</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18763,7 +18763,7 @@
         <v>44825</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18836,7 +18836,7 @@
         <v>45590</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18909,7 +18909,7 @@
         <v>46293</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18982,7 +18982,7 @@
         <v>44804</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -19055,7 +19055,7 @@
         <v>45159</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -19128,7 +19128,7 @@
         <v>45306</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -19201,7 +19201,7 @@
         <v>45721</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19274,7 +19274,7 @@
         <v>46253</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19347,7 +19347,7 @@
         <v>45315</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19420,7 +19420,7 @@
         <v>45737</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19493,7 +19493,7 @@
         <v>45547</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19566,7 +19566,7 @@
         <v>45775</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19639,7 +19639,7 @@
         <v>45715</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19712,7 +19712,7 @@
         <v>45743</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19785,7 +19785,7 @@
         <v>45710</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19858,7 +19858,7 @@
         <v>45792</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19931,7 +19931,7 @@
         <v>45334</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20004,7 +20004,7 @@
         <v>45142</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -20077,7 +20077,7 @@
         <v>45734</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -20155,7 +20155,7 @@
         <v>45796</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20228,7 +20228,7 @@
         <v>45799</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20306,7 +20306,7 @@
         <v>45799</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20384,7 +20384,7 @@
         <v>45803</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20457,7 +20457,7 @@
         <v>45800</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20535,7 +20535,7 @@
         <v>45800</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20608,7 +20608,7 @@
         <v>45810</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20681,7 +20681,7 @@
         <v>45810</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20754,7 +20754,7 @@
         <v>45810</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20827,7 +20827,7 @@
         <v>46269</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20900,7 +20900,7 @@
         <v>45821</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20973,7 +20973,7 @@
         <v>45821</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -21046,7 +21046,7 @@
         <v>45824</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -21124,7 +21124,7 @@
         <v>45821</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -21197,7 +21197,7 @@
         <v>45821</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -21270,7 +21270,7 @@
         <v>45827</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -21348,7 +21348,7 @@
         <v>45842</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21421,7 +21421,7 @@
         <v>45846</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21494,7 +21494,7 @@
         <v>45846</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21567,7 +21567,7 @@
         <v>45846</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21640,7 +21640,7 @@
         <v>45769</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21713,7 +21713,7 @@
         <v>44986</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21811,7 +21811,7 @@
         <v>45716</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>

--- a/Översikt SKÖVDE.xlsx
+++ b/Översikt SKÖVDE.xlsx
@@ -601,7 +601,7 @@
         <v>46196</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -736,7 +736,7 @@
         <v>46198</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -852,7 +852,7 @@
         <v>45876</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -966,7 +966,7 @@
         <v>45743</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1080,7 +1080,7 @@
         <v>46182</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1190,7 +1190,7 @@
         <v>44495</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1300,7 +1300,7 @@
         <v>46014</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1409,7 +1409,7 @@
         <v>46080</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1518,7 +1518,7 @@
         <v>45201</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1627,7 +1627,7 @@
         <v>44595</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1744,7 +1744,7 @@
         <v>44594</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1861,7 +1861,7 @@
         <v>45979</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1973,7 +1973,7 @@
         <v>45306</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2089,7 +2089,7 @@
         <v>44949</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2206,7 +2206,7 @@
         <v>45714</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2323,7 +2323,7 @@
         <v>45387</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2431,7 +2431,7 @@
         <v>44928</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2543,7 +2543,7 @@
         <v>44837</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2650,7 +2650,7 @@
         <v>44804</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2762,7 +2762,7 @@
         <v>45506</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2869,7 +2869,7 @@
         <v>46289</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2976,7 +2976,7 @@
         <v>45824</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3088,7 +3088,7 @@
         <v>45334</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3199,7 +3199,7 @@
         <v>45334</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3310,7 +3310,7 @@
         <v>44943</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3417,7 +3417,7 @@
         <v>44817</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3524,7 +3524,7 @@
         <v>44750</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3635,7 +3635,7 @@
         <v>45797</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3750,7 +3750,7 @@
         <v>46185</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3856,7 +3856,7 @@
         <v>45972</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3962,7 +3962,7 @@
         <v>45635</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4068,7 +4068,7 @@
         <v>45785</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4178,7 +4178,7 @@
         <v>45743</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4284,7 +4284,7 @@
         <v>45903</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4395,7 +4395,7 @@
         <v>45800</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4506,7 +4506,7 @@
         <v>45471</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4612,7 +4612,7 @@
         <v>45799</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4723,7 +4723,7 @@
         <v>44495</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4829,7 +4829,7 @@
         <v>44988</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4940,7 +4940,7 @@
         <v>44834</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5050,7 +5050,7 @@
         <v>45036</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5155,7 +5155,7 @@
         <v>45040</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5260,7 +5260,7 @@
         <v>45932</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5365,7 +5365,7 @@
         <v>45148</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5470,7 +5470,7 @@
         <v>45182</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5580,7 +5580,7 @@
         <v>46173</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5685,7 +5685,7 @@
         <v>45322</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5790,7 +5790,7 @@
         <v>46045</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5895,7 +5895,7 @@
         <v>46052</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6000,7 +6000,7 @@
         <v>45810</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6110,7 +6110,7 @@
         <v>45019</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6215,7 +6215,7 @@
         <v>46272</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6320,7 +6320,7 @@
         <v>45322</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6425,7 +6425,7 @@
         <v>46198</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6530,7 +6530,7 @@
         <v>45645</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6635,7 +6635,7 @@
         <v>45755</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6745,7 +6745,7 @@
         <v>45104</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6855,7 +6855,7 @@
         <v>44988</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6960,7 +6960,7 @@
         <v>45204</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7065,7 +7065,7 @@
         <v>45224</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7170,7 +7170,7 @@
         <v>44986</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7280,7 +7280,7 @@
         <v>44594</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7358,7 +7358,7 @@
         <v>44609</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7431,7 +7431,7 @@
         <v>44543</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7509,7 +7509,7 @@
         <v>44516</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7582,7 +7582,7 @@
         <v>44844</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7655,7 +7655,7 @@
         <v>44567</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7728,7 +7728,7 @@
         <v>44523</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7801,7 +7801,7 @@
         <v>44748</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7874,7 +7874,7 @@
         <v>44748</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7947,7 +7947,7 @@
         <v>44585</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8020,7 +8020,7 @@
         <v>44614</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8098,7 +8098,7 @@
         <v>44698</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8171,7 +8171,7 @@
         <v>44740</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8244,7 +8244,7 @@
         <v>44530</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8317,7 +8317,7 @@
         <v>44698</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8390,7 +8390,7 @@
         <v>44847</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8463,7 +8463,7 @@
         <v>44635</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8536,7 +8536,7 @@
         <v>44823</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8609,7 +8609,7 @@
         <v>44629</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8682,7 +8682,7 @@
         <v>44762</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8755,7 +8755,7 @@
         <v>45888</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8833,7 +8833,7 @@
         <v>44809</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8906,7 +8906,7 @@
         <v>45853</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8979,7 +8979,7 @@
         <v>45756</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9052,7 +9052,7 @@
         <v>45635</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9125,7 +9125,7 @@
         <v>45267</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9198,7 +9198,7 @@
         <v>45889</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9271,7 +9271,7 @@
         <v>45889</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9344,7 +9344,7 @@
         <v>45709</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9417,7 +9417,7 @@
         <v>45322</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9490,7 +9490,7 @@
         <v>45884</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9568,7 +9568,7 @@
         <v>44862</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9641,7 +9641,7 @@
         <v>45013</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9714,7 +9714,7 @@
         <v>45267</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9787,7 +9787,7 @@
         <v>46038</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9860,7 +9860,7 @@
         <v>44523</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9938,7 +9938,7 @@
         <v>45105</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10011,7 +10011,7 @@
         <v>45138</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10084,7 +10084,7 @@
         <v>45929</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10157,7 +10157,7 @@
         <v>45905</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10230,7 +10230,7 @@
         <v>45324</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10303,7 +10303,7 @@
         <v>45932</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10376,7 +10376,7 @@
         <v>45937</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10449,7 +10449,7 @@
         <v>45086</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10522,7 +10522,7 @@
         <v>46174</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10595,7 +10595,7 @@
         <v>44495</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10668,7 +10668,7 @@
         <v>45299</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10741,7 +10741,7 @@
         <v>45301</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10814,7 +10814,7 @@
         <v>45245</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10887,7 +10887,7 @@
         <v>45315</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10960,7 +10960,7 @@
         <v>45947</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11033,7 +11033,7 @@
         <v>45947</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11106,7 +11106,7 @@
         <v>45947</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11179,7 +11179,7 @@
         <v>45953</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11257,7 +11257,7 @@
         <v>46182</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11330,7 +11330,7 @@
         <v>46182</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11403,7 +11403,7 @@
         <v>45958</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11476,7 +11476,7 @@
         <v>46185</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11549,7 +11549,7 @@
         <v>44903</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11627,7 +11627,7 @@
         <v>45530</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11700,7 +11700,7 @@
         <v>45210</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11773,7 +11773,7 @@
         <v>45320</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11846,7 +11846,7 @@
         <v>45197</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11919,7 +11919,7 @@
         <v>45687</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11992,7 +11992,7 @@
         <v>45215</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12065,7 +12065,7 @@
         <v>44743</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12138,7 +12138,7 @@
         <v>45706</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12211,7 +12211,7 @@
         <v>46202</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12284,7 +12284,7 @@
         <v>45082</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12357,7 +12357,7 @@
         <v>45742</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12430,7 +12430,7 @@
         <v>45093</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12503,7 +12503,7 @@
         <v>45989</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12581,7 +12581,7 @@
         <v>45989</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12659,7 +12659,7 @@
         <v>45314</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12732,7 +12732,7 @@
         <v>45306</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12805,7 +12805,7 @@
         <v>46129</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12878,7 +12878,7 @@
         <v>45259</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12951,7 +12951,7 @@
         <v>46001</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13024,7 +13024,7 @@
         <v>46002</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13097,7 +13097,7 @@
         <v>45775</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13170,7 +13170,7 @@
         <v>46002</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13243,7 +13243,7 @@
         <v>46001</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13316,7 +13316,7 @@
         <v>46001</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13389,7 +13389,7 @@
         <v>46008</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13462,7 +13462,7 @@
         <v>46008</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13535,7 +13535,7 @@
         <v>46013</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13608,7 +13608,7 @@
         <v>46017</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13681,7 +13681,7 @@
         <v>45792</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13754,7 +13754,7 @@
         <v>46283</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13827,7 +13827,7 @@
         <v>45710</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13900,7 +13900,7 @@
         <v>45743</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13973,7 +13973,7 @@
         <v>45715</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14046,7 +14046,7 @@
         <v>45142</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14119,7 +14119,7 @@
         <v>46036</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14192,7 +14192,7 @@
         <v>45734</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14270,7 +14270,7 @@
         <v>45796</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14343,7 +14343,7 @@
         <v>45334</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14416,7 +14416,7 @@
         <v>45799</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14494,7 +14494,7 @@
         <v>45800</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14572,7 +14572,7 @@
         <v>46288</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14645,7 +14645,7 @@
         <v>45800</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14718,7 +14718,7 @@
         <v>45799</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14796,7 +14796,7 @@
         <v>45803</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14869,7 +14869,7 @@
         <v>46052</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14942,7 +14942,7 @@
         <v>46051</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15015,7 +15015,7 @@
         <v>45159</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15088,7 +15088,7 @@
         <v>45810</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15161,7 +15161,7 @@
         <v>46009</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15239,7 +15239,7 @@
         <v>45810</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15312,7 +15312,7 @@
         <v>46010</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15390,7 +15390,7 @@
         <v>45810</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15463,7 +15463,7 @@
         <v>46009</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15541,7 +15541,7 @@
         <v>46010</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15619,7 +15619,7 @@
         <v>46293</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15692,7 +15692,7 @@
         <v>46062</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15765,7 +15765,7 @@
         <v>45992</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15838,7 +15838,7 @@
         <v>46062</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15911,7 +15911,7 @@
         <v>45824</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15989,7 +15989,7 @@
         <v>45821</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16062,7 +16062,7 @@
         <v>45821</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16135,7 +16135,7 @@
         <v>45821</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16208,7 +16208,7 @@
         <v>45821</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16281,7 +16281,7 @@
         <v>46253</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16354,7 +16354,7 @@
         <v>45827</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16432,7 +16432,7 @@
         <v>46091</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16505,7 +16505,7 @@
         <v>44938</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16578,7 +16578,7 @@
         <v>45842</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16651,7 +16651,7 @@
         <v>46099</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16724,7 +16724,7 @@
         <v>45531</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16797,7 +16797,7 @@
         <v>45846</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16870,7 +16870,7 @@
         <v>45846</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16943,7 +16943,7 @@
         <v>45846</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17016,7 +17016,7 @@
         <v>45315</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17089,7 +17089,7 @@
         <v>45769</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17162,7 +17162,7 @@
         <v>45721</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17235,7 +17235,7 @@
         <v>45894</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17308,7 +17308,7 @@
         <v>45847</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17381,7 +17381,7 @@
         <v>45586</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17454,7 +17454,7 @@
         <v>45586</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17527,7 +17527,7 @@
         <v>45670</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17600,7 +17600,7 @@
         <v>45547</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17673,7 +17673,7 @@
         <v>45693</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17746,7 +17746,7 @@
         <v>46269</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17819,7 +17819,7 @@
         <v>44938</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17892,7 +17892,7 @@
         <v>45401</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17965,7 +17965,7 @@
         <v>44599</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -18043,7 +18043,7 @@
         <v>46272</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -18116,7 +18116,7 @@
         <v>45376</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -18189,7 +18189,7 @@
         <v>45685</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18262,7 +18262,7 @@
         <v>45439</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18335,7 +18335,7 @@
         <v>44750</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18413,7 +18413,7 @@
         <v>46149</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18486,7 +18486,7 @@
         <v>45590</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18559,7 +18559,7 @@
         <v>46139</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18632,7 +18632,7 @@
         <v>45594</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18705,7 +18705,7 @@
         <v>44825</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18778,7 +18778,7 @@
         <v>45076</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18851,7 +18851,7 @@
         <v>45699</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18929,7 +18929,7 @@
         <v>45006</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19002,7 +19002,7 @@
         <v>45161</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -19075,7 +19075,7 @@
         <v>45002</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -19148,7 +19148,7 @@
         <v>45590</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -19221,7 +19221,7 @@
         <v>44820</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19294,7 +19294,7 @@
         <v>45201</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19367,7 +19367,7 @@
         <v>44739</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19440,7 +19440,7 @@
         <v>45706</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19513,7 +19513,7 @@
         <v>45721</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19586,7 +19586,7 @@
         <v>45259</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19659,7 +19659,7 @@
         <v>44804</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19732,7 +19732,7 @@
         <v>45093</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19805,7 +19805,7 @@
         <v>44959</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19878,7 +19878,7 @@
         <v>45418</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19951,7 +19951,7 @@
         <v>45693</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20024,7 +20024,7 @@
         <v>45306</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -20097,7 +20097,7 @@
         <v>45539</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -20170,7 +20170,7 @@
         <v>45169</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20243,7 +20243,7 @@
         <v>45560</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20316,7 +20316,7 @@
         <v>45590</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20389,7 +20389,7 @@
         <v>45230</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20462,7 +20462,7 @@
         <v>45163</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20535,7 +20535,7 @@
         <v>45385</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20608,7 +20608,7 @@
         <v>45204</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20681,7 +20681,7 @@
         <v>45749</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20759,7 +20759,7 @@
         <v>44811</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20832,7 +20832,7 @@
         <v>45134</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20905,7 +20905,7 @@
         <v>45694</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20978,7 +20978,7 @@
         <v>45211</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -21051,7 +21051,7 @@
         <v>44586</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -21124,7 +21124,7 @@
         <v>45301</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -21197,7 +21197,7 @@
         <v>44796</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -21270,7 +21270,7 @@
         <v>44636</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -21343,7 +21343,7 @@
         <v>45737</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21416,7 +21416,7 @@
         <v>45636</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21489,7 +21489,7 @@
         <v>44601</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21567,7 +21567,7 @@
         <v>44963</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21640,7 +21640,7 @@
         <v>44600</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21713,7 +21713,7 @@
         <v>44986</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21811,7 +21811,7 @@
         <v>45716</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>

--- a/Översikt SKÖVDE.xlsx
+++ b/Översikt SKÖVDE.xlsx
@@ -601,7 +601,7 @@
         <v>46196</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -736,7 +736,7 @@
         <v>46198</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -852,7 +852,7 @@
         <v>45876</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -966,7 +966,7 @@
         <v>45743</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1080,7 +1080,7 @@
         <v>46182</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1190,7 +1190,7 @@
         <v>44495</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1300,7 +1300,7 @@
         <v>46014</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1409,7 +1409,7 @@
         <v>46080</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1518,7 +1518,7 @@
         <v>45201</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1627,7 +1627,7 @@
         <v>44595</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1744,7 +1744,7 @@
         <v>44594</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1861,7 +1861,7 @@
         <v>45979</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1973,7 +1973,7 @@
         <v>45306</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2089,7 +2089,7 @@
         <v>44949</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2206,7 +2206,7 @@
         <v>45714</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2323,7 +2323,7 @@
         <v>45387</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2431,7 +2431,7 @@
         <v>44928</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2543,7 +2543,7 @@
         <v>44837</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2650,7 +2650,7 @@
         <v>44804</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2762,7 +2762,7 @@
         <v>45506</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2869,7 +2869,7 @@
         <v>46289</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2976,7 +2976,7 @@
         <v>45824</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3088,7 +3088,7 @@
         <v>45334</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3199,7 +3199,7 @@
         <v>45334</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3310,7 +3310,7 @@
         <v>44943</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3417,7 +3417,7 @@
         <v>44817</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3524,7 +3524,7 @@
         <v>44750</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3635,7 +3635,7 @@
         <v>45797</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3750,7 +3750,7 @@
         <v>46185</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3856,7 +3856,7 @@
         <v>45972</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3962,7 +3962,7 @@
         <v>45635</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4068,7 +4068,7 @@
         <v>45785</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4178,7 +4178,7 @@
         <v>45743</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4284,7 +4284,7 @@
         <v>45903</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4395,7 +4395,7 @@
         <v>45800</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4506,7 +4506,7 @@
         <v>45471</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4612,7 +4612,7 @@
         <v>45799</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4723,7 +4723,7 @@
         <v>44495</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4829,7 +4829,7 @@
         <v>44988</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4940,7 +4940,7 @@
         <v>44834</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5050,7 +5050,7 @@
         <v>45036</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5155,7 +5155,7 @@
         <v>45040</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5260,7 +5260,7 @@
         <v>45932</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5365,7 +5365,7 @@
         <v>45148</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5470,7 +5470,7 @@
         <v>45182</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5580,7 +5580,7 @@
         <v>46173</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5685,7 +5685,7 @@
         <v>45322</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5790,7 +5790,7 @@
         <v>46045</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5895,7 +5895,7 @@
         <v>46052</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6000,7 +6000,7 @@
         <v>45810</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6110,7 +6110,7 @@
         <v>45019</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6215,7 +6215,7 @@
         <v>46272</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6320,7 +6320,7 @@
         <v>45322</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6425,7 +6425,7 @@
         <v>46198</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6530,7 +6530,7 @@
         <v>45645</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6635,7 +6635,7 @@
         <v>45755</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6745,7 +6745,7 @@
         <v>45104</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6855,7 +6855,7 @@
         <v>44988</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6960,7 +6960,7 @@
         <v>45204</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7065,7 +7065,7 @@
         <v>45224</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7170,7 +7170,7 @@
         <v>44986</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7280,7 +7280,7 @@
         <v>44594</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7358,7 +7358,7 @@
         <v>44609</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7431,7 +7431,7 @@
         <v>44543</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7509,7 +7509,7 @@
         <v>44516</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7582,7 +7582,7 @@
         <v>44844</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7655,7 +7655,7 @@
         <v>44567</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7728,7 +7728,7 @@
         <v>44523</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7801,7 +7801,7 @@
         <v>44748</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7874,7 +7874,7 @@
         <v>44748</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7947,7 +7947,7 @@
         <v>44585</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8020,7 +8020,7 @@
         <v>44614</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8098,7 +8098,7 @@
         <v>44698</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8171,7 +8171,7 @@
         <v>44740</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8244,7 +8244,7 @@
         <v>44530</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8317,7 +8317,7 @@
         <v>44698</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8390,7 +8390,7 @@
         <v>44847</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8463,7 +8463,7 @@
         <v>44635</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8536,7 +8536,7 @@
         <v>44823</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8609,7 +8609,7 @@
         <v>44629</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8682,7 +8682,7 @@
         <v>44762</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8755,7 +8755,7 @@
         <v>45888</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8833,7 +8833,7 @@
         <v>44809</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8906,7 +8906,7 @@
         <v>45853</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8979,7 +8979,7 @@
         <v>45756</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9052,7 +9052,7 @@
         <v>45635</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9125,7 +9125,7 @@
         <v>45267</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9198,7 +9198,7 @@
         <v>45889</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9271,7 +9271,7 @@
         <v>45889</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9344,7 +9344,7 @@
         <v>45709</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9417,7 +9417,7 @@
         <v>45322</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9490,7 +9490,7 @@
         <v>45884</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9568,7 +9568,7 @@
         <v>44862</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9641,7 +9641,7 @@
         <v>45013</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9714,7 +9714,7 @@
         <v>45267</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9787,7 +9787,7 @@
         <v>46038</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9860,7 +9860,7 @@
         <v>44523</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9938,7 +9938,7 @@
         <v>45105</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10011,7 +10011,7 @@
         <v>45138</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10084,7 +10084,7 @@
         <v>45929</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10157,7 +10157,7 @@
         <v>45905</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10230,7 +10230,7 @@
         <v>45324</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10303,7 +10303,7 @@
         <v>45932</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10376,7 +10376,7 @@
         <v>45937</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10449,7 +10449,7 @@
         <v>45086</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10522,7 +10522,7 @@
         <v>46174</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10595,7 +10595,7 @@
         <v>44495</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10668,7 +10668,7 @@
         <v>45299</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10741,7 +10741,7 @@
         <v>45301</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10814,7 +10814,7 @@
         <v>45245</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10887,7 +10887,7 @@
         <v>45315</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10960,7 +10960,7 @@
         <v>45947</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11033,7 +11033,7 @@
         <v>45947</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11106,7 +11106,7 @@
         <v>45947</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11179,7 +11179,7 @@
         <v>45953</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11257,7 +11257,7 @@
         <v>46182</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11330,7 +11330,7 @@
         <v>46182</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11403,7 +11403,7 @@
         <v>45958</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11476,7 +11476,7 @@
         <v>46185</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11549,7 +11549,7 @@
         <v>44903</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11627,7 +11627,7 @@
         <v>45530</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11700,7 +11700,7 @@
         <v>45210</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11773,7 +11773,7 @@
         <v>45320</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11846,7 +11846,7 @@
         <v>45197</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11919,7 +11919,7 @@
         <v>45687</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11992,7 +11992,7 @@
         <v>45215</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12065,7 +12065,7 @@
         <v>44743</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12138,7 +12138,7 @@
         <v>45706</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12211,7 +12211,7 @@
         <v>46202</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12284,7 +12284,7 @@
         <v>45082</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12357,7 +12357,7 @@
         <v>45742</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12430,7 +12430,7 @@
         <v>45093</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12503,7 +12503,7 @@
         <v>45989</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12581,7 +12581,7 @@
         <v>45989</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12659,7 +12659,7 @@
         <v>45314</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12732,7 +12732,7 @@
         <v>45306</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12805,7 +12805,7 @@
         <v>46129</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12878,7 +12878,7 @@
         <v>45259</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12951,7 +12951,7 @@
         <v>46001</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13024,7 +13024,7 @@
         <v>46002</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13097,7 +13097,7 @@
         <v>45775</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13170,7 +13170,7 @@
         <v>46002</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13243,7 +13243,7 @@
         <v>46001</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13316,7 +13316,7 @@
         <v>46001</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13389,7 +13389,7 @@
         <v>46008</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13462,7 +13462,7 @@
         <v>46008</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13535,7 +13535,7 @@
         <v>46013</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13608,7 +13608,7 @@
         <v>46017</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13681,7 +13681,7 @@
         <v>45792</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13754,7 +13754,7 @@
         <v>46283</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13827,7 +13827,7 @@
         <v>45710</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13900,7 +13900,7 @@
         <v>45743</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13973,7 +13973,7 @@
         <v>45715</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14046,7 +14046,7 @@
         <v>45142</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14119,7 +14119,7 @@
         <v>46036</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14192,7 +14192,7 @@
         <v>45734</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14270,7 +14270,7 @@
         <v>45796</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14343,7 +14343,7 @@
         <v>45334</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14416,7 +14416,7 @@
         <v>45799</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14494,7 +14494,7 @@
         <v>45800</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14572,7 +14572,7 @@
         <v>46288</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14645,7 +14645,7 @@
         <v>45800</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14718,7 +14718,7 @@
         <v>45799</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14796,7 +14796,7 @@
         <v>45803</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14869,7 +14869,7 @@
         <v>46052</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14942,7 +14942,7 @@
         <v>46051</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15015,7 +15015,7 @@
         <v>45159</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15088,7 +15088,7 @@
         <v>45810</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15161,7 +15161,7 @@
         <v>46009</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15239,7 +15239,7 @@
         <v>45810</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15312,7 +15312,7 @@
         <v>46010</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15390,7 +15390,7 @@
         <v>45810</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15463,7 +15463,7 @@
         <v>46009</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15541,7 +15541,7 @@
         <v>46010</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15619,7 +15619,7 @@
         <v>46293</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15692,7 +15692,7 @@
         <v>46062</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15765,7 +15765,7 @@
         <v>45992</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15838,7 +15838,7 @@
         <v>46062</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15911,7 +15911,7 @@
         <v>45824</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15989,7 +15989,7 @@
         <v>45821</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16062,7 +16062,7 @@
         <v>45821</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16135,7 +16135,7 @@
         <v>45821</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16208,7 +16208,7 @@
         <v>45821</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16281,7 +16281,7 @@
         <v>46253</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16354,7 +16354,7 @@
         <v>45827</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16432,7 +16432,7 @@
         <v>46091</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16505,7 +16505,7 @@
         <v>44938</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16578,7 +16578,7 @@
         <v>45842</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16651,7 +16651,7 @@
         <v>46099</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16724,7 +16724,7 @@
         <v>45531</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16797,7 +16797,7 @@
         <v>45846</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16870,7 +16870,7 @@
         <v>45846</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16943,7 +16943,7 @@
         <v>45846</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17016,7 +17016,7 @@
         <v>45315</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17089,7 +17089,7 @@
         <v>45769</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17162,7 +17162,7 @@
         <v>45721</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17235,7 +17235,7 @@
         <v>45894</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17308,7 +17308,7 @@
         <v>45847</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17381,7 +17381,7 @@
         <v>45586</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17454,7 +17454,7 @@
         <v>45586</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17527,7 +17527,7 @@
         <v>45670</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17600,7 +17600,7 @@
         <v>45547</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17673,7 +17673,7 @@
         <v>45693</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17746,7 +17746,7 @@
         <v>46269</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17819,7 +17819,7 @@
         <v>44938</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17892,7 +17892,7 @@
         <v>45401</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17965,7 +17965,7 @@
         <v>44599</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -18043,7 +18043,7 @@
         <v>46272</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -18116,7 +18116,7 @@
         <v>45376</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -18189,7 +18189,7 @@
         <v>45685</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18262,7 +18262,7 @@
         <v>45439</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18335,7 +18335,7 @@
         <v>44750</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18413,7 +18413,7 @@
         <v>46149</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18486,7 +18486,7 @@
         <v>45590</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18559,7 +18559,7 @@
         <v>46139</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18632,7 +18632,7 @@
         <v>45594</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18705,7 +18705,7 @@
         <v>44825</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18778,7 +18778,7 @@
         <v>45076</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18851,7 +18851,7 @@
         <v>45699</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18929,7 +18929,7 @@
         <v>45006</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19002,7 +19002,7 @@
         <v>45161</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -19075,7 +19075,7 @@
         <v>45002</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -19148,7 +19148,7 @@
         <v>45590</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -19221,7 +19221,7 @@
         <v>44820</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19294,7 +19294,7 @@
         <v>45201</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19367,7 +19367,7 @@
         <v>44739</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19440,7 +19440,7 @@
         <v>45706</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19513,7 +19513,7 @@
         <v>45721</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19586,7 +19586,7 @@
         <v>45259</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19659,7 +19659,7 @@
         <v>44804</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19732,7 +19732,7 @@
         <v>45093</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19805,7 +19805,7 @@
         <v>44959</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19878,7 +19878,7 @@
         <v>45418</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19951,7 +19951,7 @@
         <v>45693</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20024,7 +20024,7 @@
         <v>45306</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -20097,7 +20097,7 @@
         <v>45539</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -20170,7 +20170,7 @@
         <v>45169</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20243,7 +20243,7 @@
         <v>45560</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20316,7 +20316,7 @@
         <v>45590</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20389,7 +20389,7 @@
         <v>45230</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20462,7 +20462,7 @@
         <v>45163</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20535,7 +20535,7 @@
         <v>45385</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20608,7 +20608,7 @@
         <v>45204</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20681,7 +20681,7 @@
         <v>45749</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20759,7 +20759,7 @@
         <v>44811</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20832,7 +20832,7 @@
         <v>45134</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20905,7 +20905,7 @@
         <v>45694</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20978,7 +20978,7 @@
         <v>45211</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -21051,7 +21051,7 @@
         <v>44586</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -21124,7 +21124,7 @@
         <v>45301</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -21197,7 +21197,7 @@
         <v>44796</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -21270,7 +21270,7 @@
         <v>44636</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -21343,7 +21343,7 @@
         <v>45737</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21416,7 +21416,7 @@
         <v>45636</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21489,7 +21489,7 @@
         <v>44601</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21567,7 +21567,7 @@
         <v>44963</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21640,7 +21640,7 @@
         <v>44600</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21713,7 +21713,7 @@
         <v>44986</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21811,7 +21811,7 @@
         <v>45716</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
